--- a/Results/Phase 2/Carbon dioxide/carbon dioxide water use results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide water use results.xlsx
@@ -2165,7 +2165,7 @@
         <v>0.01997717397982315</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02330093021131269</v>
+        <v>0.02330093021131268</v>
       </c>
       <c r="H3" t="n">
         <v>0.02216929157747203</v>
@@ -2338,7 +2338,7 @@
         <v>0.03549086955370924</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03759925446345986</v>
+        <v>0.03759925446345987</v>
       </c>
       <c r="G5" t="n">
         <v>0.03727588184805587</v>
@@ -2854,16 +2854,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03859534687507372</v>
+        <v>0.03859534687507373</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03859534687507372</v>
+        <v>0.03859534687507373</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03859534687507372</v>
+        <v>0.03859534687507373</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03859534687507372</v>
+        <v>0.03859534687507373</v>
       </c>
       <c r="F11" t="n">
         <v>0.03859534687507437</v>
@@ -2872,16 +2872,16 @@
         <v>0.03859534687507437</v>
       </c>
       <c r="H11" t="n">
-        <v>0.03859534687507372</v>
+        <v>0.03859534687507373</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03859534687507372</v>
+        <v>0.03859534687507373</v>
       </c>
       <c r="J11" t="n">
         <v>0.03842346990082667</v>
       </c>
       <c r="K11" t="n">
-        <v>0.03859534687507372</v>
+        <v>0.03859534687507373</v>
       </c>
       <c r="L11" t="n">
         <v>0.03859534687507375</v>
@@ -2890,25 +2890,25 @@
         <v>0.03859534687507437</v>
       </c>
       <c r="N11" t="n">
-        <v>0.03859534687507372</v>
+        <v>0.03859534687507373</v>
       </c>
       <c r="O11" t="n">
         <v>0.03859534687507437</v>
       </c>
       <c r="P11" t="n">
-        <v>0.03859534687507372</v>
+        <v>0.03859534687507373</v>
       </c>
       <c r="Q11" t="n">
         <v>0.03859534687507437</v>
       </c>
       <c r="R11" t="n">
-        <v>0.03859534687507372</v>
+        <v>0.03859534687507373</v>
       </c>
       <c r="S11" t="n">
         <v>0.04255234049779924</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03859534687507372</v>
+        <v>0.03859534687507373</v>
       </c>
       <c r="U11" t="n">
         <v>0.03859534687507437</v>
@@ -2923,13 +2923,13 @@
         <v>0.03859534687507437</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.03859534687507372</v>
+        <v>0.03859534687507373</v>
       </c>
       <c r="Z11" t="n">
         <v>0.03859534687507437</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.03859534687507372</v>
+        <v>0.03859534687507373</v>
       </c>
       <c r="AB11" t="n">
         <v>0.03859534687507437</v>
@@ -3142,7 +3142,7 @@
         <v>0.020242024953763</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01835036293775882</v>
+        <v>0.01835036293775881</v>
       </c>
       <c r="K14" t="n">
         <v>0.020242024953763</v>
@@ -5014,85 +5014,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05148433470065826</v>
+        <v>0.05148433470065653</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7121146984406758</v>
+        <v>0.7121146984406752</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3725557716485051</v>
+        <v>0.3725557716485028</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5891236513563327</v>
+        <v>0.5891236513563333</v>
       </c>
       <c r="F2" t="n">
-        <v>0.871031523209168</v>
+        <v>0.8710315232091674</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09969641816479613</v>
+        <v>0.09969641816479764</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1400605244295574</v>
+        <v>0.1400605244295563</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2543213930139205</v>
+        <v>0.254321393013919</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1699228451420169</v>
+        <v>0.1699228451420153</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2056087053930696</v>
+        <v>0.2056087053930681</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2449167741711798</v>
+        <v>0.244916774171178</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1593258235744331</v>
+        <v>0.1593258235744329</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04838133337390092</v>
+        <v>0.04838133337389978</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1241650849968207</v>
+        <v>0.1241650849968196</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1504125010875587</v>
+        <v>0.1504125010875576</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05333284298494107</v>
+        <v>0.05333284298493961</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3546587886720763</v>
+        <v>0.354658788672075</v>
       </c>
       <c r="S2" t="n">
-        <v>0.235837817417561</v>
+        <v>0.2358378174175595</v>
       </c>
       <c r="T2" t="n">
-        <v>0.08735149089290258</v>
+        <v>0.08735149089290112</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1533439752579793</v>
+        <v>0.1533439752579769</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1951236781737086</v>
+        <v>0.1951236781737083</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1259607028099928</v>
+        <v>0.1259607028099912</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2372310063354543</v>
+        <v>0.2372310063354529</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09933639333531226</v>
+        <v>0.09933639333531115</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.08656383861496117</v>
+        <v>0.08656383861495963</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.231410638594603</v>
+        <v>0.2314106385946013</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.09355659716817348</v>
+        <v>0.0935565971681734</v>
       </c>
     </row>
     <row r="3">
@@ -5102,82 +5102,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01764608812472101</v>
+        <v>0.0176460881247193</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02504405124434067</v>
+        <v>0.0250440512443407</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02322788726395418</v>
+        <v>0.02322788726395432</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01986228103325844</v>
+        <v>0.01986228103325849</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0206188708006912</v>
+        <v>0.02061887080069122</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02438530967745214</v>
+        <v>0.02438530967745275</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02322788726395418</v>
+        <v>0.02322788726395432</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02322788726395418</v>
+        <v>0.02322788726395432</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02272133510820284</v>
+        <v>0.02272133510820199</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02322788726395418</v>
+        <v>0.02322788726395432</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02322788726395418</v>
+        <v>0.02322788726395432</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02271198161082685</v>
+        <v>0.02271198161082688</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01890105911619733</v>
+        <v>0.01890105911619603</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0200901090600051</v>
+        <v>0.02009010906000502</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01979864418734803</v>
+        <v>0.01979864418734847</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01654913719575326</v>
+        <v>0.01654913719575115</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02322788726395418</v>
+        <v>0.02322788726395432</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02322788726395418</v>
+        <v>0.02322788726395432</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02322788726395418</v>
+        <v>0.02322788726395432</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02050482064994504</v>
+        <v>0.02050482064994428</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02044559509977044</v>
+        <v>0.02044559509977019</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0232289842466184</v>
+        <v>0.0232289842466168</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01706072017756827</v>
+        <v>0.01706072017756698</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02878002697468694</v>
+        <v>0.02878002697468648</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01754240334009355</v>
+        <v>0.01754240334009315</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02322788726395418</v>
+        <v>0.02322788726395432</v>
       </c>
       <c r="AB3" t="n">
         <v>0.02841659473386857</v>
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05114143136233001</v>
+        <v>0.05114143136232688</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2930876349681873</v>
+        <v>0.2930876349681857</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1681681999186578</v>
+        <v>0.1681681999186532</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2468545987473489</v>
+        <v>0.2468545987473485</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3511933685534125</v>
+        <v>0.3511933685534099</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06871416965014278</v>
+        <v>0.06871416965013845</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08342641240437947</v>
+        <v>0.08342641240437722</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1250731572845218</v>
+        <v>0.1250731572845178</v>
       </c>
       <c r="J4" t="n">
-        <v>0.09395846915564122</v>
+        <v>0.09395846915563789</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1073179546599794</v>
+        <v>0.1073179546599763</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1216452841509541</v>
+        <v>0.1216452841509484</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09012052361749433</v>
+        <v>0.0901205236174895</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05001042381600755</v>
+        <v>0.05001042381600458</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07763271138482135</v>
+        <v>0.07763271138481896</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08719958633717437</v>
+        <v>0.08719958633717018</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05181519092567149</v>
+        <v>0.0518151909256668</v>
       </c>
       <c r="R4" t="n">
-        <v>0.161644959780734</v>
+        <v>0.16164495978073</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1183361110247514</v>
+        <v>0.1183361110247457</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06421458862099157</v>
+        <v>0.06421458862098707</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08826807424918764</v>
+        <v>0.08826807424918473</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1024932913378846</v>
+        <v>0.1024932913378852</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07828719299251388</v>
+        <v>0.07828719299250997</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1188439120256728</v>
+        <v>0.1188439120256715</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06858294482741907</v>
+        <v>0.06858294482741559</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06392749861476119</v>
+        <v>0.06392749861475645</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1167224563303417</v>
+        <v>0.1167224563303374</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.06606831120175947</v>
+        <v>0.06606831120175362</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03880778783414961</v>
+        <v>0.03880778783414876</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04265845205599771</v>
+        <v>0.04265845205599443</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04084228807560999</v>
+        <v>0.04084228807560601</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03936551386909003</v>
+        <v>0.03936551386909085</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04122794280006398</v>
+        <v>0.04122794280005714</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04126415495418834</v>
+        <v>0.04126415495418714</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04084228807560999</v>
+        <v>0.04084228807560601</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04084228807560999</v>
+        <v>0.04084228807560601</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04030524727571194</v>
+        <v>0.04030524727571196</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04084228807560999</v>
+        <v>0.04084228807560601</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04084228807560999</v>
+        <v>0.04084228807560601</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04032638242248569</v>
+        <v>0.04032638242248132</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03926521002393481</v>
+        <v>0.03926521002393014</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03969860476592371</v>
+        <v>0.03969860476591936</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03959236924239194</v>
+        <v>0.03959236924238815</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03840796210159222</v>
+        <v>0.03840796210158769</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04084228807560999</v>
+        <v>0.04084228807560601</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04084228807560999</v>
+        <v>0.04084228807560601</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04084228807560999</v>
+        <v>0.04084228807560601</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03984976227066418</v>
+        <v>0.03984976227066417</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03882518123104569</v>
+        <v>0.03882518123104733</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04084268791290997</v>
+        <v>0.04084268791290516</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03859442809115484</v>
+        <v>0.03859442809114947</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04286597780365311</v>
+        <v>0.04286597780365096</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0387699959476883</v>
+        <v>0.03876999594768131</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04084228807560999</v>
+        <v>0.04084228807560601</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04232554522697907</v>
+        <v>0.04232554522697918</v>
       </c>
     </row>
     <row r="6">
@@ -5366,85 +5366,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0266747532847123</v>
+        <v>0.02667475328471134</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2686209568905671</v>
+        <v>0.2686209568905672</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1437015218410393</v>
+        <v>0.1437015218410385</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2223879206697325</v>
+        <v>0.2223879206697328</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3267266904757927</v>
+        <v>0.3267266904757926</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04196958756434774</v>
+        <v>0.04196958756434641</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05895973432676298</v>
+        <v>0.05895973432676214</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1006064792069041</v>
+        <v>0.100606479206903</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06732137124968694</v>
+        <v>0.0673213712496864</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08285127658236154</v>
+        <v>0.08285127658236077</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09717860607333498</v>
+        <v>0.09717860607333383</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06565384553987466</v>
+        <v>0.06565384553987461</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0255437457383905</v>
+        <v>0.02554374573838968</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05088812929902715</v>
+        <v>0.05088812929902592</v>
       </c>
       <c r="P6" t="n">
-        <v>0.06045500425138015</v>
+        <v>0.06045500425137915</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02734851284805314</v>
+        <v>0.02734851284805209</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1371782817031162</v>
+        <v>0.1371782817031154</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09386943294713383</v>
+        <v>0.09386943294713286</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03974791054337329</v>
+        <v>0.03974791054337236</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06152349216339098</v>
+        <v>0.06152349216338996</v>
       </c>
       <c r="V6" t="n">
-        <v>0.07605700699200095</v>
+        <v>0.07605700699200119</v>
       </c>
       <c r="W6" t="n">
-        <v>0.05154261090671926</v>
+        <v>0.05154261090671818</v>
       </c>
       <c r="X6" t="n">
-        <v>0.09209932993987845</v>
+        <v>0.09209932993987721</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.04411626674980166</v>
+        <v>0.04411626674980063</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03946082053714342</v>
+        <v>0.03946082053714241</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.09225577825272369</v>
+        <v>0.09225577825272276</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.04160163312413926</v>
+        <v>0.04160163312413925</v>
       </c>
     </row>
     <row r="7">
@@ -5454,85 +5454,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01434110975653575</v>
+        <v>0.0143411097565347</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01819177397837754</v>
+        <v>0.01819177397837759</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01637560999799076</v>
+        <v>0.01637560999799077</v>
       </c>
       <c r="E7" t="n">
         <v>0.01489883579147377</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01676126472244205</v>
+        <v>0.01676126472244208</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01451957286839333</v>
+        <v>0.01451957286839421</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01637560999799076</v>
+        <v>0.01637560999799077</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01637560999799076</v>
+        <v>0.01637560999799077</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01366814936976292</v>
+        <v>0.01366814936976137</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01637560999799076</v>
+        <v>0.01637560999799077</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01637560999799076</v>
+        <v>0.01637560999799077</v>
       </c>
       <c r="M7" t="n">
         <v>0.01585970434486517</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01479853194631564</v>
+        <v>0.01479853194631394</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01295402268012743</v>
+        <v>0.01295402268012625</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0128477871565975</v>
+        <v>0.01284778715659623</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01394128402397405</v>
+        <v>0.01394128402397407</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01637560999799076</v>
+        <v>0.01637560999799077</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01637560999799076</v>
+        <v>0.01637560999799077</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01637560999799076</v>
+        <v>0.01637560999799077</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01310518018486998</v>
+        <v>0.01310518018486996</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01238889688516163</v>
+        <v>0.01238889688516165</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01409810582711354</v>
+        <v>0.01409810582711312</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01184984600535968</v>
+        <v>0.01184984600535805</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01839929972603585</v>
+        <v>0.01839929972603688</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01430331787006803</v>
+        <v>0.01430331787006611</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01637560999799076</v>
+        <v>0.01637560999799077</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01785886714936246</v>
+        <v>0.01785886714936247</v>
       </c>
     </row>
     <row r="8">
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03524058586882326</v>
+        <v>0.03524058586882327</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03050936943164518</v>
+        <v>0.03050936943164521</v>
       </c>
     </row>
     <row r="9">
@@ -5630,85 +5630,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05552367493531567</v>
+        <v>0.05552367493531554</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7635532651701749</v>
+        <v>0.763553265170174</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4005801081774057</v>
+        <v>0.4005801081774059</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6337491116967823</v>
+        <v>0.6337491116967832</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9340331695418728</v>
+        <v>0.9340331695418718</v>
       </c>
       <c r="G9" t="n">
-        <v>0.107337345180944</v>
+        <v>0.107337345180946</v>
       </c>
       <c r="H9" t="n">
         <v>0.1507167708661543</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2735132679562014</v>
+        <v>0.2735132679562015</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1833542893358824</v>
+        <v>0.1833542893358827</v>
       </c>
       <c r="K9" t="n">
-        <v>0.221161596926626</v>
+        <v>0.2211615969266263</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2634060959675438</v>
+        <v>0.2634060959675432</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1719756908053286</v>
+        <v>0.1719756908053284</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05218887013195263</v>
+        <v>0.05218887013195272</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1336338945828726</v>
+        <v>0.1336338945828728</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1618420711313273</v>
+        <v>0.1618420711313274</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05751027231518986</v>
+        <v>0.05751027231518976</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3813461670634112</v>
+        <v>0.3813461670634114</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2536489139997448</v>
+        <v>0.2536489139997445</v>
       </c>
       <c r="T9" t="n">
         <v>0.09407021493240389</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1649925351869353</v>
+        <v>0.1649925351869357</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2112454710589227</v>
+        <v>0.2112454710589233</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1355636504153099</v>
+        <v>0.1355636504153096</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2551461782952243</v>
+        <v>0.2551461782952244</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1069504254202776</v>
+        <v>0.1069504254202775</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.09322372267434094</v>
+        <v>0.09322372267434074</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.2488910116821272</v>
+        <v>0.2488910116821268</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.1014287651416781</v>
+        <v>0.1014287651416782</v>
       </c>
     </row>
     <row r="10">
@@ -5718,85 +5718,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01915761016900034</v>
+        <v>0.01915761016900038</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02515638639265692</v>
+        <v>0.02515638639265697</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02515638639265692</v>
+        <v>0.02515638639265697</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02196221500658634</v>
+        <v>0.02196221500658639</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02009214939538001</v>
+        <v>0.02009214939538007</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02640027172095928</v>
+        <v>0.02640027172095933</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02515638639265692</v>
+        <v>0.02515638639265697</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02515638639265692</v>
+        <v>0.02515638639265697</v>
       </c>
       <c r="J10" t="n">
-        <v>0.02515638639265692</v>
+        <v>0.02515638639265697</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02515638639265692</v>
+        <v>0.02515638639265697</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02515638639265692</v>
+        <v>0.02515638639265697</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02515638639265462</v>
+        <v>0.02515638639265465</v>
       </c>
       <c r="N10" t="n">
-        <v>0.02050633124571091</v>
+        <v>0.02050633124571096</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02178420677539854</v>
+        <v>0.02178420677539856</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02147096860531953</v>
+        <v>0.02147096860531959</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01797871372592362</v>
+        <v>0.01797871372592366</v>
       </c>
       <c r="R10" t="n">
-        <v>0.02515638639265692</v>
+        <v>0.02515638639265697</v>
       </c>
       <c r="S10" t="n">
-        <v>0.02515638639265692</v>
+        <v>0.02515638639265697</v>
       </c>
       <c r="T10" t="n">
-        <v>0.02515638639265692</v>
+        <v>0.02515638639265697</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02222989856103035</v>
+        <v>0.02222989856103041</v>
       </c>
       <c r="V10" t="n">
-        <v>0.02351841291874575</v>
+        <v>0.02351841291874579</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02515756532320456</v>
+        <v>0.0251575653232046</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01852851348603539</v>
+        <v>0.01852851348603541</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.03112328753982499</v>
+        <v>0.03112328753982501</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01904617982096082</v>
+        <v>0.01904617982096086</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.02515638639265692</v>
+        <v>0.02515638639265697</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.031422609766937</v>
+        <v>0.03142260976693707</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04290743730855032</v>
+        <v>0.04290743730854348</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="S11" t="n">
-        <v>0.04525916744846965</v>
+        <v>0.04525916744846582</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="V11" t="n">
-        <v>0.04275874827977214</v>
+        <v>0.04275874827977039</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0429336542374467</v>
+        <v>0.04293365423743895</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05522882159784248</v>
+        <v>0.05522882159784157</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4032433729821903</v>
+        <v>0.4032433729821865</v>
       </c>
       <c r="D12" t="n">
-        <v>0.224832834584356</v>
+        <v>0.2248328345843531</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3394413301553042</v>
+        <v>0.339441330155299</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4870385819088124</v>
+        <v>0.4870385819088127</v>
       </c>
       <c r="G12" t="n">
-        <v>0.08069655833484529</v>
+        <v>0.08069655833484458</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1020186493566927</v>
+        <v>0.1020186493566873</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1623762508408152</v>
+        <v>0.1623762508408122</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1180346028472135</v>
+        <v>0.1180346028472098</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1366440730351742</v>
+        <v>0.1366440730351722</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1574083187460133</v>
+        <v>0.1574083187460112</v>
       </c>
       <c r="M12" t="n">
-        <v>0.11246794919894</v>
+        <v>0.1124679491989347</v>
       </c>
       <c r="N12" t="n">
-        <v>0.05358968022069775</v>
+        <v>0.05358968022069516</v>
       </c>
       <c r="O12" t="n">
-        <v>0.09362198118339148</v>
+        <v>0.09362198118338744</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1074870173941313</v>
+        <v>0.1074870173941266</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.05620528473649186</v>
+        <v>0.05620528473649029</v>
       </c>
       <c r="R12" t="n">
-        <v>0.215378863337309</v>
+        <v>0.2153788633373052</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1526124156479913</v>
+        <v>0.1526124156479893</v>
       </c>
       <c r="T12" t="n">
-        <v>0.07417542638600712</v>
+        <v>0.07417542638600336</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1090355506052933</v>
+        <v>0.1090355506052892</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1315951390101492</v>
+        <v>0.1315951390101501</v>
       </c>
       <c r="W12" t="n">
-        <v>0.09457050525578836</v>
+        <v>0.09457050525578449</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1533483591301296</v>
+        <v>0.1533483591301271</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.08050637743169156</v>
+        <v>0.08050637743168809</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.07375935391177305</v>
+        <v>0.07375935391177044</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1502737856480107</v>
+        <v>0.1502737856480088</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.07779234096872936</v>
+        <v>0.07779234096872657</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03735397584306971</v>
+        <v>0.03735397584306365</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04030252692783156</v>
+        <v>0.04030252692782507</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04030252692783156</v>
+        <v>0.04030252692782507</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03873251045211018</v>
+        <v>0.03873251045210629</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03781332564158657</v>
+        <v>0.03781332564158631</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04091392820324888</v>
+        <v>0.04091392820324551</v>
       </c>
       <c r="H13" t="n">
-        <v>0.04030252692783156</v>
+        <v>0.04030252692782507</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04030252692783156</v>
+        <v>0.04030252692782507</v>
       </c>
       <c r="J13" t="n">
-        <v>0.04027630999893508</v>
+        <v>0.04027630999893107</v>
       </c>
       <c r="K13" t="n">
-        <v>0.04030252692783156</v>
+        <v>0.04030252692782507</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04030252692783156</v>
+        <v>0.04030252692782507</v>
       </c>
       <c r="M13" t="n">
-        <v>0.04030252692783048</v>
+        <v>0.04030252692782407</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03801690655518558</v>
+        <v>0.03801690655518088</v>
       </c>
       <c r="O13" t="n">
-        <v>0.03864501487907868</v>
+        <v>0.03864501487907784</v>
       </c>
       <c r="P13" t="n">
-        <v>0.03849105035169176</v>
+        <v>0.03849105035168651</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.03677451825764442</v>
+        <v>0.03677451825764471</v>
       </c>
       <c r="R13" t="n">
-        <v>0.04030252692783156</v>
+        <v>0.04030252692782507</v>
       </c>
       <c r="S13" t="n">
-        <v>0.04030252692783156</v>
+        <v>0.04030252692782507</v>
       </c>
       <c r="T13" t="n">
-        <v>0.04030252692783156</v>
+        <v>0.04030252692782507</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03886408372728915</v>
+        <v>0.03886408372728964</v>
       </c>
       <c r="V13" t="n">
-        <v>0.03932251534807031</v>
+        <v>0.03932251534806865</v>
       </c>
       <c r="W13" t="n">
-        <v>0.04030310640217972</v>
+        <v>0.04030310640217637</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03704475882316298</v>
+        <v>0.0370447588231577</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.04323541060179897</v>
+        <v>0.04323541060179904</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.03729920499292345</v>
+        <v>0.03729920499292095</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.04030252692783156</v>
+        <v>0.04030252692782507</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.04338253508928467</v>
+        <v>0.04338253508928403</v>
       </c>
     </row>
     <row r="14">
@@ -6070,85 +6070,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01993672095895667</v>
+        <v>0.01993672095895671</v>
       </c>
       <c r="H14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02000292731028708</v>
+        <v>0.02000292731028714</v>
       </c>
       <c r="K14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="N14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01993672095895667</v>
+        <v>0.01993672095895671</v>
       </c>
       <c r="P14" t="n">
-        <v>0.01993672095895667</v>
+        <v>0.01993672095895671</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="R14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02422094140731167</v>
+        <v>0.0242209414073117</v>
       </c>
       <c r="T14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01993672095895667</v>
+        <v>0.01993672095895672</v>
       </c>
       <c r="V14" t="n">
-        <v>0.02002691178016086</v>
+        <v>0.02002691178016087</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01993672095895667</v>
+        <v>0.01993672095895671</v>
       </c>
       <c r="X14" t="n">
-        <v>0.01993672095895667</v>
+        <v>0.01993672095895671</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.02189542819628809</v>
+        <v>0.02189542819628815</v>
       </c>
     </row>
     <row r="15">
@@ -6158,85 +6158,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03419059555668506</v>
+        <v>0.03419059555668501</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3822051469410324</v>
+        <v>0.3822051469410329</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2037946085431989</v>
+        <v>0.2037946085431988</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3184031041141464</v>
+        <v>0.3184031041141466</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4660003558676598</v>
+        <v>0.466000355867659</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05769962505635717</v>
+        <v>0.05769962505635674</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0809804233155349</v>
+        <v>0.08098042331553498</v>
       </c>
       <c r="I15" t="n">
         <v>0.1413380247996577</v>
       </c>
       <c r="J15" t="n">
-        <v>0.09513009284895595</v>
+        <v>0.09513009284895585</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1156058469940164</v>
+        <v>0.1156058469940163</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1363700927048551</v>
+        <v>0.136370092704855</v>
       </c>
       <c r="M15" t="n">
-        <v>0.09142972315778254</v>
+        <v>0.09142972315778251</v>
       </c>
       <c r="N15" t="n">
         <v>0.03255145417954034</v>
       </c>
       <c r="O15" t="n">
-        <v>0.07062504790490183</v>
+        <v>0.07062504790490204</v>
       </c>
       <c r="P15" t="n">
         <v>0.0844900841156408</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.03516705869533571</v>
+        <v>0.03516705869533568</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1943406372961515</v>
+        <v>0.1943406372961513</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1315741896068331</v>
+        <v>0.131574189606833</v>
       </c>
       <c r="T15" t="n">
-        <v>0.05313720034484912</v>
+        <v>0.05313720034484916</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08603861732680443</v>
+        <v>0.08603861732680411</v>
       </c>
       <c r="V15" t="n">
         <v>0.1088633025105382</v>
       </c>
       <c r="W15" t="n">
-        <v>0.07157357197729862</v>
+        <v>0.07157357197729863</v>
       </c>
       <c r="X15" t="n">
-        <v>0.130351425851641</v>
+        <v>0.1303514258516411</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.05946815139053404</v>
+        <v>0.05946815139053417</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.05272112787061461</v>
+        <v>0.05272112787061452</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.1292355596068545</v>
+        <v>0.1292355596068543</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.05675411492757174</v>
+        <v>0.05675411492757178</v>
       </c>
     </row>
     <row r="16">
@@ -6246,85 +6246,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01631574980191188</v>
+        <v>0.01631574980191193</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01926430088667436</v>
+        <v>0.01926430088667441</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01926430088667436</v>
+        <v>0.01926430088667441</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0176942844109514</v>
+        <v>0.01769428441095143</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01677509960043047</v>
+        <v>0.01677509960043051</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01791699492476012</v>
+        <v>0.01791699492476016</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01926430088667436</v>
+        <v>0.01926430088667441</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01926430088667436</v>
+        <v>0.01926430088667441</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01737180000067334</v>
+        <v>0.01737180000067337</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01926430088667436</v>
+        <v>0.01926430088667441</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01926430088667436</v>
+        <v>0.01926430088667441</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01926430088667324</v>
+        <v>0.01926430088667328</v>
       </c>
       <c r="N16" t="n">
-        <v>0.01697868051402849</v>
+        <v>0.01697868051402853</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0156480816005903</v>
+        <v>0.01564808160059034</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01549411707320331</v>
+        <v>0.01549411707320334</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01573629221648832</v>
+        <v>0.01573629221648831</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01926430088667436</v>
+        <v>0.01926430088667441</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01926430088667436</v>
+        <v>0.01926430088667441</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01926430088667436</v>
+        <v>0.01926430088667441</v>
       </c>
       <c r="U16" t="n">
-        <v>0.01586715044880174</v>
+        <v>0.01586715044880177</v>
       </c>
       <c r="V16" t="n">
-        <v>0.01659067884845924</v>
+        <v>0.01659067884845926</v>
       </c>
       <c r="W16" t="n">
-        <v>0.01730617312369156</v>
+        <v>0.01730617312369158</v>
       </c>
       <c r="X16" t="n">
-        <v>0.01404782554467191</v>
+        <v>0.01404782554467195</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.02219718456064292</v>
+        <v>0.02219718456064296</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.01626097895176888</v>
+        <v>0.01626097895176892</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.01926430088667436</v>
+        <v>0.01926430088667441</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.02234430904812825</v>
+        <v>0.0223443090481283</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04818417852995714</v>
+        <v>0.04818417852995709</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7306228760971017</v>
+        <v>0.7306228760971016</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2974160636693091</v>
+        <v>0.2974160636693056</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5359262888774473</v>
+        <v>0.5359262888774486</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7697105271678919</v>
+        <v>0.7697105271678912</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09067170350975609</v>
+        <v>0.0906717035097525</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1193445647936339</v>
+        <v>0.1193445647936333</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1726355800559144</v>
+        <v>0.1726355800559131</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1611924848648356</v>
+        <v>0.1611924848648346</v>
       </c>
       <c r="K2" t="n">
-        <v>0.16844373506267</v>
+        <v>0.1684437350626698</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2422676868965449</v>
+        <v>0.2422676868965422</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1883657204553056</v>
+        <v>0.188365720455305</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04339106539586196</v>
+        <v>0.04339106539586431</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1084764024615581</v>
+        <v>0.1084764024615612</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1249259202317779</v>
+        <v>0.1249259202317786</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05724077987837124</v>
+        <v>0.05724077987837057</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2785118603997853</v>
+        <v>0.2785118603997834</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2112124418977334</v>
+        <v>0.2112124418977324</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0943033007954423</v>
+        <v>0.09430330079544144</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1095607764816078</v>
+        <v>0.1095607764816074</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1684400982723423</v>
+        <v>0.1684400982723414</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1068529912716854</v>
+        <v>0.1068529912716861</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2428619163196605</v>
+        <v>0.2428619163196589</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0814026881557721</v>
+        <v>0.08140268815577195</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0687222950881072</v>
+        <v>0.06872229508810596</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.186261690741977</v>
+        <v>0.1862616907419757</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.09188311906656439</v>
+        <v>0.09188311906656417</v>
       </c>
     </row>
     <row r="3">
@@ -6578,85 +6578,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01714711089353014</v>
+        <v>0.01714711089352916</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02463552778548766</v>
+        <v>0.02463552778548762</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02266480398128144</v>
+        <v>0.02266480398128088</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01935284064470456</v>
+        <v>0.01935284064470449</v>
       </c>
       <c r="F3" t="n">
         <v>0.01987841780176574</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02380893358739332</v>
+        <v>0.02380893358739233</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02266480398128144</v>
+        <v>0.02266480398128088</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02266480398128144</v>
+        <v>0.02266480398128088</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02219895258959848</v>
+        <v>0.02219895258960103</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02266480398128144</v>
+        <v>0.02266480398128088</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02266480398128144</v>
+        <v>0.02266480398128088</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02234337554961617</v>
+        <v>0.0223433755496161</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01838766874813021</v>
+        <v>0.01838766874812983</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01956306264752754</v>
+        <v>0.01956306264752639</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01927494520133199</v>
+        <v>0.01927494520133195</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01606275826683026</v>
+        <v>0.01606275826682895</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02266480398128144</v>
+        <v>0.02266480398128088</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02266480398128144</v>
+        <v>0.02266480398128088</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02266480398128144</v>
+        <v>0.02266480398128088</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01997441053395313</v>
+        <v>0.01997441053395489</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01997772561832128</v>
+        <v>0.01997772561832082</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02266588836526394</v>
+        <v>0.02266588836526378</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01656846580164319</v>
+        <v>0.01656846580164231</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02815557188355713</v>
+        <v>0.02815557188355752</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01704461691172073</v>
+        <v>0.01704461691172319</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02266480398128144</v>
+        <v>0.02266480398128088</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02790099310864059</v>
+        <v>0.02790099310864052</v>
       </c>
     </row>
     <row r="4">
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04796929112482577</v>
+        <v>0.04796929112483002</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2979626009072511</v>
+        <v>0.2979626009072549</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1388113866295624</v>
+        <v>0.1388113866295626</v>
       </c>
       <c r="E4" t="n">
-        <v>0.225507910494899</v>
+        <v>0.2255079104949033</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3121466693549416</v>
+        <v>0.3121466693549437</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06345549506625459</v>
+        <v>0.0634554950662541</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07390641631049133</v>
+        <v>0.07390641631049276</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09333036559889729</v>
+        <v>0.09333036559889943</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08879050883019918</v>
+        <v>0.08879050883020179</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09180248732198644</v>
+        <v>0.09180248732199055</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1187104508808288</v>
+        <v>0.1187104508808272</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09885954551911574</v>
+        <v>0.09885954551911774</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04622225767102477</v>
+        <v>0.04622225767102509</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06994509876085842</v>
+        <v>0.06994509876085631</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07594075482810969</v>
+        <v>0.07594075482810975</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05127031596834071</v>
+        <v>0.0512703159683401</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1319210265221857</v>
+        <v>0.1319210265221865</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1073911787478607</v>
+        <v>0.1073911787478584</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06477916963251736</v>
+        <v>0.06477916963251948</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07034034035780291</v>
+        <v>0.07034034035780146</v>
       </c>
       <c r="V4" t="n">
-        <v>0.09056342132168767</v>
+        <v>0.09056342132168717</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06935338444520255</v>
+        <v>0.06935338444520703</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1189270405277577</v>
+        <v>0.1189270405277585</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0600770478120013</v>
+        <v>0.06007704781200177</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05545519343953087</v>
+        <v>0.05545519343952921</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0982969229380969</v>
+        <v>0.09829692293810122</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.06356180766161751</v>
+        <v>0.06356180766161638</v>
       </c>
     </row>
     <row r="5">
@@ -6754,85 +6754,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03665664442699856</v>
+        <v>0.03665664442699629</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04063850256966466</v>
+        <v>0.04063850256966678</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0386677787654584</v>
+        <v>0.0386677787654605</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03722295452574768</v>
+        <v>0.03722295452575136</v>
       </c>
       <c r="F5" t="n">
-        <v>0.038841670464161</v>
+        <v>0.03884167046416463</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0390848005718374</v>
+        <v>0.0390848005718399</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0386677787654584</v>
+        <v>0.0386677787654605</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0386677787654584</v>
+        <v>0.0386677787654605</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03812899846033272</v>
+        <v>0.03812899846033627</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0386677787654584</v>
+        <v>0.0386677787654605</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0386677787654584</v>
+        <v>0.0386677787654605</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03834635033379335</v>
+        <v>0.03834635033379635</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03710881319763183</v>
+        <v>0.03710881319763436</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03753723047178958</v>
+        <v>0.03753723047179159</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0374322150458973</v>
+        <v>0.03743221504589878</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03626141062767551</v>
+        <v>0.03626141062767935</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0386677787654584</v>
+        <v>0.0386677787654605</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0386677787654584</v>
+        <v>0.0386677787654605</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0386677787654584</v>
+        <v>0.0386677787654605</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03768716194609956</v>
+        <v>0.03768716194610563</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03645062982249328</v>
+        <v>0.03645062982249387</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03866817401068693</v>
+        <v>0.03866817401069022</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03644573508579718</v>
+        <v>0.03644573508579756</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04066909918998378</v>
+        <v>0.04066909918998882</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03661928657417089</v>
+        <v>0.03661928657417179</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0386677787654584</v>
+        <v>0.0386677787654605</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04024107406600817</v>
+        <v>0.04024107406600843</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02521948255600382</v>
+        <v>0.02521948255600239</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2752127923384306</v>
+        <v>0.2752127923384304</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1160615780607397</v>
+        <v>0.1160615780607406</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2027581019260768</v>
+        <v>0.2027581019260773</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2893968607861195</v>
+        <v>0.2893968607861191</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03842719764871429</v>
+        <v>0.03842719764871274</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05115660774166959</v>
+        <v>0.05115660774166877</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07058055703007522</v>
+        <v>0.07058055703007401</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06391206209844007</v>
+        <v>0.06391206209844176</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06905267875316153</v>
+        <v>0.06905267875316672</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09596064231200327</v>
+        <v>0.09596064231200291</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0761097369502932</v>
+        <v>0.07610973695029274</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02347244910220385</v>
+        <v>0.02347244910220132</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0449168013433176</v>
+        <v>0.04491680134331665</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05091245741057067</v>
+        <v>0.05091245741056905</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0285205073995169</v>
+        <v>0.02852050739951644</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1091712179533635</v>
+        <v>0.1091712179533611</v>
       </c>
       <c r="S6" t="n">
-        <v>0.08464137017903753</v>
+        <v>0.08464137017903479</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04202936106369548</v>
+        <v>0.04202936106369538</v>
       </c>
       <c r="U6" t="n">
-        <v>0.04531204294026172</v>
+        <v>0.04531204294026051</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06612636507500097</v>
+        <v>0.06612636507500065</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04432508702766434</v>
+        <v>0.04432508702766517</v>
       </c>
       <c r="X6" t="n">
-        <v>0.09389874311021919</v>
+        <v>0.09389874311021675</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0373272392431773</v>
+        <v>0.03732723924317734</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03270538487070684</v>
+        <v>0.03270538487070641</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.07554711436927632</v>
+        <v>0.07554711436927504</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.04081199909279522</v>
+        <v>0.04081199909279518</v>
       </c>
     </row>
     <row r="7">
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01390683585817352</v>
+        <v>0.013906835858174</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01788869400084193</v>
+        <v>0.01788869400084192</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01591797019663527</v>
+        <v>0.01591797019663594</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01447314595692621</v>
+        <v>0.01447314595692618</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01609186189533894</v>
+        <v>0.01609186189533892</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01405650315429724</v>
+        <v>0.01405650315429729</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01591797019663527</v>
+        <v>0.01591797019663594</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01591797019663527</v>
+        <v>0.01591797019663594</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01325055172857767</v>
+        <v>0.01325055172857814</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01591797019663527</v>
+        <v>0.01591797019663594</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01591797019663527</v>
+        <v>0.01591797019663594</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01559654176497104</v>
+        <v>0.01559654176497101</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01435900462880991</v>
+        <v>0.01435900462880873</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01250893305425233</v>
+        <v>0.0125089330542497</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0124039176283571</v>
+        <v>0.01240391762835778</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01351160205885246</v>
+        <v>0.01351160205885225</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01591797019663527</v>
+        <v>0.01591797019663594</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01591797019663527</v>
+        <v>0.01591797019663594</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01591797019663527</v>
+        <v>0.01591797019663594</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01265886452856054</v>
+        <v>0.0126588645285622</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01201357357580747</v>
+        <v>0.0120135735758076</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01363987659314784</v>
+        <v>0.01363987659314701</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01141743766825709</v>
+        <v>0.01141743766825619</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01791929062116178</v>
+        <v>0.01791929062116286</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0138694780053488</v>
+        <v>0.01386947800534886</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01591797019663527</v>
+        <v>0.01591797019663594</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01749126549718717</v>
+        <v>0.01749126549718712</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091013</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03287301847075865</v>
+        <v>0.03287301847075864</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0286658420509102</v>
+        <v>0.02866584205091008</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05204098852899135</v>
+        <v>0.05204098852899136</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7833419544266574</v>
+        <v>0.7833419544266568</v>
       </c>
       <c r="D9" t="n">
-        <v>0.319891240653274</v>
+        <v>0.3198912406532735</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5766207828440713</v>
+        <v>0.5766207828440725</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8254559751585723</v>
+        <v>0.8254559751585697</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0977024586559488</v>
+        <v>0.09770245865594585</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1285172684051789</v>
+        <v>0.1285172684051787</v>
       </c>
       <c r="I9" t="n">
         <v>0.1857892818394948</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1739920051080116</v>
+        <v>0.1739920051080108</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1812842934922848</v>
+        <v>0.1812842934922846</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2606231152504151</v>
+        <v>0.2606231152504149</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2030399508539548</v>
+        <v>0.2030399508539539</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04688981551311081</v>
+        <v>0.04688981551311079</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1168372218527674</v>
+        <v>0.1168372218527671</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1345155677819475</v>
+        <v>0.1345155677819491</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06177414507597754</v>
+        <v>0.06177414507597759</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2995748368788547</v>
+        <v>0.2995748368788543</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2272479505997844</v>
+        <v>0.2272479505997838</v>
       </c>
       <c r="T9" t="n">
         <v>0.1016053471167933</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1180026018542235</v>
+        <v>0.1180026018542224</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1825506931111777</v>
+        <v>0.182550693111177</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1150925369932586</v>
+        <v>0.1150925369932584</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2612617353880932</v>
+        <v>0.2612617353880928</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.08774102014209335</v>
+        <v>0.08774102014209056</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.07411336379984539</v>
+        <v>0.07411336379984547</v>
       </c>
       <c r="AA9" t="n">
         <v>0.2004333037337833</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.09957127928844876</v>
+        <v>0.09957127928844846</v>
       </c>
     </row>
     <row r="10">
@@ -7194,85 +7194,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0186853591440619</v>
+        <v>0.01868535914406182</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02461524040252215</v>
+        <v>0.02461524040252209</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02461524040252215</v>
+        <v>0.02461524040252209</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02145775355314421</v>
+        <v>0.02145775355314418</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01960916534005745</v>
+        <v>0.0196091653400574</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02584483991098076</v>
+        <v>0.0258448399109807</v>
       </c>
       <c r="H10" t="n">
-        <v>0.02461524040252215</v>
+        <v>0.02461524040252209</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02461524040252215</v>
+        <v>0.02461524040252209</v>
       </c>
       <c r="J10" t="n">
-        <v>0.02461524040252215</v>
+        <v>0.02461524040252209</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02461524040252215</v>
+        <v>0.02461524040252209</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02461524040252215</v>
+        <v>0.02461524040252209</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02461524040252095</v>
+        <v>0.02461524040252097</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0200185903794785</v>
+        <v>0.02001859037947841</v>
       </c>
       <c r="O10" t="n">
-        <v>0.02128178971740644</v>
+        <v>0.02128178971740639</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02097214903655389</v>
+        <v>0.0209721490365538</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01752000213409842</v>
+        <v>0.0175200021340984</v>
       </c>
       <c r="R10" t="n">
-        <v>0.02461524040252215</v>
+        <v>0.02461524040252209</v>
       </c>
       <c r="S10" t="n">
-        <v>0.02461524040252215</v>
+        <v>0.02461524040252209</v>
       </c>
       <c r="T10" t="n">
-        <v>0.02461524040252215</v>
+        <v>0.02461524040252209</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02172386652081756</v>
+        <v>0.02172386652081749</v>
       </c>
       <c r="V10" t="n">
-        <v>0.02299773734023017</v>
+        <v>0.02299773734023009</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02461640579323055</v>
+        <v>0.02461640579323045</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01806348753375078</v>
+        <v>0.01806348753375071</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.03051618508365018</v>
+        <v>0.03051618508365006</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01857520855537214</v>
+        <v>0.01857520855537212</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.02461524040252215</v>
+        <v>0.02461524040252209</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.03080949722474672</v>
+        <v>0.03080949722474663</v>
       </c>
     </row>
     <row r="11">
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="H11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0403040234685059</v>
+        <v>0.04030402346850712</v>
       </c>
       <c r="K11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.04036673358549089</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="N11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="P11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="R11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="S11" t="n">
-        <v>0.04243466779973901</v>
+        <v>0.04243466779974123</v>
       </c>
       <c r="T11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="U11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0399483538539546</v>
+        <v>0.03994835385395488</v>
       </c>
       <c r="W11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.04036673358548881</v>
+        <v>0.0403667335854908</v>
       </c>
     </row>
     <row r="12">
@@ -7370,85 +7370,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05185621259499532</v>
+        <v>0.05185621259499534</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4113092369938721</v>
+        <v>0.4113092369938742</v>
       </c>
       <c r="D12" t="n">
-        <v>0.183511423926342</v>
+        <v>0.183511423926346</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3097005234850242</v>
+        <v>0.3097005234850281</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4320093492972941</v>
+        <v>0.432009349297297</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07429998650070412</v>
+        <v>0.0742999865007053</v>
       </c>
       <c r="H12" t="n">
-        <v>0.08944624922584668</v>
+        <v>0.08944624922585019</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1175969004657338</v>
+        <v>0.1175969004657343</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1117355287873023</v>
+        <v>0.1117355287873025</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1153825841147375</v>
+        <v>0.1153825841147415</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1543796328854813</v>
+        <v>0.1543796328854839</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1260760430339926</v>
+        <v>0.1260760430339951</v>
       </c>
       <c r="N12" t="n">
-        <v>0.04932428004450611</v>
+        <v>0.04932428004450917</v>
       </c>
       <c r="O12" t="n">
-        <v>0.08370520927900348</v>
+        <v>0.08370520927900499</v>
       </c>
       <c r="P12" t="n">
-        <v>0.09239456592823533</v>
+        <v>0.09239456592823905</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.05664030658763323</v>
+        <v>0.05664030658763586</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1735253947507072</v>
+        <v>0.1735253947507063</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1379748906071043</v>
+        <v>0.1379748906071071</v>
       </c>
       <c r="T12" t="n">
-        <v>0.07621835544394814</v>
+        <v>0.07621835544394989</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0842780231895969</v>
+        <v>0.08427802318960005</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1155866720050705</v>
+        <v>0.1155866720050686</v>
       </c>
       <c r="W12" t="n">
-        <v>0.08284765229683308</v>
+        <v>0.08284765229683178</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1546935309255981</v>
+        <v>0.1546935309255999</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.06940368611530368</v>
+        <v>0.06940368611530411</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.06270534642190925</v>
+        <v>0.06270534642191251</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1247948096778517</v>
+        <v>0.124794809677856</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.07521855937252601</v>
+        <v>0.07521855937252879</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03546107239656277</v>
+        <v>0.03546107239656394</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0383757598536802</v>
+        <v>0.03837575985368216</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0383757598536802</v>
+        <v>0.03837575985368216</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03682377476076341</v>
+        <v>0.0368237747607657</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03591514663766746</v>
+        <v>0.03591514663766828</v>
       </c>
       <c r="G13" t="n">
-        <v>0.03898013928530398</v>
+        <v>0.0389801392853061</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0383757598536802</v>
+        <v>0.03837575985368216</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0383757598536802</v>
+        <v>0.03837575985368216</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03831304973669832</v>
+        <v>0.03831304973669913</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0383757598536802</v>
+        <v>0.03837575985368216</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0383757598536802</v>
+        <v>0.03837575985368216</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03837575985367962</v>
+        <v>0.03837575985368157</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03611638945771957</v>
+        <v>0.03611638945771916</v>
       </c>
       <c r="O13" t="n">
-        <v>0.036737284060094</v>
+        <v>0.03673728406009485</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0365850877901595</v>
+        <v>0.0365850877901619</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.03488826978687191</v>
+        <v>0.0348882697868735</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0383757598536802</v>
+        <v>0.03837575985368216</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0383757598536802</v>
+        <v>0.03837575985368216</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0383757598536802</v>
+        <v>0.03837575985368216</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03695457605260175</v>
+        <v>0.03695457605260331</v>
       </c>
       <c r="V13" t="n">
-        <v>0.03716233622800714</v>
+        <v>0.03716233622800771</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03837633267285333</v>
+        <v>0.03837633267285492</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0351554066836236</v>
+        <v>0.03515540668362432</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0412762242470756</v>
+        <v>0.04127622424707784</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.03540693058068884</v>
+        <v>0.03540693058069019</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0383757598536802</v>
+        <v>0.03837575985368216</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.04142039462442576</v>
+        <v>0.04142039462442988</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0188455864634689</v>
+        <v>0.0188455864634688</v>
       </c>
       <c r="H14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01891172938770864</v>
+        <v>0.01891172938770857</v>
       </c>
       <c r="K14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="N14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0188455864634689</v>
+        <v>0.0188455864634688</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0188455864634689</v>
+        <v>0.0188455864634688</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="R14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02287273080340522</v>
+        <v>0.02287273080340518</v>
       </c>
       <c r="T14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01884558646346889</v>
+        <v>0.0188455864634688</v>
       </c>
       <c r="V14" t="n">
-        <v>0.01893559881384212</v>
+        <v>0.01893559881384208</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0188455864634689</v>
+        <v>0.0188455864634688</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0188455864634689</v>
+        <v>0.0188455864634688</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.02080479658915493</v>
+        <v>0.02080479658915483</v>
       </c>
     </row>
     <row r="15">
@@ -7634,85 +7634,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03229427559866128</v>
+        <v>0.03229427559866134</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3917472999975382</v>
+        <v>0.3917472999975378</v>
       </c>
       <c r="D15" t="n">
-        <v>0.163949486930008</v>
+        <v>0.1639494869300079</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2901385864886907</v>
+        <v>0.2901385864886911</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4124474123009616</v>
+        <v>0.4124474123009612</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0527788393786839</v>
+        <v>0.05277883937868272</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06988431222951326</v>
+        <v>0.06988431222951329</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09803496346940052</v>
+        <v>0.09803496346940067</v>
       </c>
       <c r="J15" t="n">
-        <v>0.09034323470650422</v>
+        <v>0.09034323470650396</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09582064711840449</v>
+        <v>0.09582064711840441</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1348176958891484</v>
+        <v>0.1348176958891482</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1065141060376593</v>
+        <v>0.1065141060376587</v>
       </c>
       <c r="N15" t="n">
-        <v>0.02976234304817257</v>
+        <v>0.02976234304817245</v>
       </c>
       <c r="O15" t="n">
-        <v>0.06218406215698313</v>
+        <v>0.06218406215698282</v>
       </c>
       <c r="P15" t="n">
-        <v>0.07087341880621581</v>
+        <v>0.07087341880621501</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.03707836959130002</v>
+        <v>0.03707836959129993</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1539634577543727</v>
+        <v>0.1539634577543729</v>
       </c>
       <c r="S15" t="n">
         <v>0.118412953610771</v>
       </c>
       <c r="T15" t="n">
-        <v>0.05665641844761382</v>
+        <v>0.05665641844761377</v>
       </c>
       <c r="U15" t="n">
-        <v>0.06275687606757746</v>
+        <v>0.06275687606757735</v>
       </c>
       <c r="V15" t="n">
-        <v>0.09457391696495523</v>
+        <v>0.09457391696495505</v>
       </c>
       <c r="W15" t="n">
-        <v>0.06132650517481315</v>
+        <v>0.06132650517481292</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1331723838035783</v>
+        <v>0.1331723838035779</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.04984174911896935</v>
+        <v>0.04984174911896823</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.04314340942557539</v>
+        <v>0.0431434094255754</v>
       </c>
       <c r="AA15" t="n">
         <v>0.1052328726815182</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.05565662237619273</v>
+        <v>0.05565662237619264</v>
       </c>
     </row>
     <row r="16">
@@ -7725,82 +7725,82 @@
         <v>0.01589913540022937</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01881382285734675</v>
+        <v>0.01881382285734669</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01881382285734675</v>
+        <v>0.01881382285734669</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01726183776443035</v>
+        <v>0.01726183776443029</v>
       </c>
       <c r="F16" t="n">
-        <v>0.01635320964133395</v>
+        <v>0.01635320964133393</v>
       </c>
       <c r="G16" t="n">
         <v>0.01745899216328403</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01881382285734675</v>
+        <v>0.01881382285734669</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01881382285734675</v>
+        <v>0.01881382285734669</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01692075565590058</v>
+        <v>0.01692075565590052</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01881382285734675</v>
+        <v>0.01881382285734669</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01881382285734675</v>
+        <v>0.01881382285734669</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01881382285734617</v>
+        <v>0.01881382285734613</v>
       </c>
       <c r="N16" t="n">
         <v>0.01655445246138667</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01521613693807475</v>
+        <v>0.0152161369380747</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01506394066813992</v>
+        <v>0.01506394066813987</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01532633279053827</v>
+        <v>0.01532633279053823</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01881382285734675</v>
+        <v>0.01881382285734669</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01881382285734675</v>
+        <v>0.01881382285734669</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01881382285734675</v>
+        <v>0.01881382285734669</v>
       </c>
       <c r="U16" t="n">
-        <v>0.01543342893058249</v>
+        <v>0.01543342893058243</v>
       </c>
       <c r="V16" t="n">
-        <v>0.01614958118789455</v>
+        <v>0.01614958118789452</v>
       </c>
       <c r="W16" t="n">
-        <v>0.01685518555083407</v>
+        <v>0.01685518555083405</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0136342595616043</v>
+        <v>0.01363425956160427</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.02171428725074232</v>
+        <v>0.02171428725074228</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0158449935843558</v>
+        <v>0.01584499358435567</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.01881382285734675</v>
+        <v>0.01881382285734669</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.02185845762809254</v>
+        <v>0.02185845762809245</v>
       </c>
     </row>
   </sheetData>
@@ -9809,7 +9809,7 @@
         <v>0.3294888799896319</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02541301722012154</v>
+        <v>0.02541301722012155</v>
       </c>
       <c r="H6" t="n">
         <v>0.05984305636229713</v>
@@ -9821,7 +9821,7 @@
         <v>0.06702877136291015</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06977242537898805</v>
+        <v>0.06977242537898803</v>
       </c>
       <c r="L6" t="n">
         <v>0.07791726928167088</v>
@@ -10155,7 +10155,7 @@
         <v>0.02430562880139231</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02117684120452979</v>
+        <v>0.0211768412045298</v>
       </c>
       <c r="F10" t="n">
         <v>0.01934505531002645</v>
@@ -10285,7 +10285,7 @@
         <v>0.03931026357385856</v>
       </c>
       <c r="S11" t="n">
-        <v>0.04476030260930449</v>
+        <v>0.04476030260930448</v>
       </c>
       <c r="T11" t="n">
         <v>0.03931026357385856</v>
@@ -10613,7 +10613,7 @@
         <v>0.09496884682875341</v>
       </c>
       <c r="K15" t="n">
-        <v>0.09703656139009141</v>
+        <v>0.0970365613900914</v>
       </c>
       <c r="L15" t="n">
         <v>0.1088406830289734</v>
@@ -10677,10 +10677,10 @@
         <v>0.01568363374206018</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01857182881604439</v>
+        <v>0.0185718288160444</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01857182881604439</v>
+        <v>0.0185718288160444</v>
       </c>
       <c r="E16" t="n">
         <v>0.01703395013566632</v>
@@ -10692,19 +10692,19 @@
         <v>0.0172144256391748</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01857182881604439</v>
+        <v>0.0185718288160444</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01857182881604439</v>
+        <v>0.0185718288160444</v>
       </c>
       <c r="J16" t="n">
         <v>0.01668158765546647</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01857182881604439</v>
+        <v>0.0185718288160444</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01857182881604439</v>
+        <v>0.0185718288160444</v>
       </c>
       <c r="M16" t="n">
         <v>0.01857182881604431</v>
@@ -10722,13 +10722,13 @@
         <v>0.01511603749030946</v>
       </c>
       <c r="R16" t="n">
-        <v>0.01857182881604439</v>
+        <v>0.0185718288160444</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01857182881604439</v>
+        <v>0.0185718288160444</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01857182881604439</v>
+        <v>0.0185718288160444</v>
       </c>
       <c r="U16" t="n">
         <v>0.01520684608823783</v>
@@ -10749,7 +10749,7 @@
         <v>0.01562998403580321</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.01857182881604439</v>
+        <v>0.0185718288160444</v>
       </c>
       <c r="AB16" t="n">
         <v>0.02158879007736688</v>

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide water use results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide water use results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06865641348012655</v>
+        <v>0.06865641348012834</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9052244563756491</v>
+        <v>0.9052244563756485</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9306359867123345</v>
+        <v>0.9306359867123338</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8369493165739923</v>
+        <v>0.8369493165739917</v>
       </c>
       <c r="F2" t="n">
-        <v>0.862763546872099</v>
+        <v>0.8627635468720989</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1119722980389272</v>
+        <v>0.1119722980389267</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1184139883258787</v>
+        <v>0.1184139883258775</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4237043107126315</v>
+        <v>0.4237043107126328</v>
       </c>
       <c r="J2" t="n">
-        <v>0.190762320596605</v>
+        <v>0.1907623205966051</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2123533876726553</v>
+        <v>0.2123533876726548</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2111751938231478</v>
+        <v>0.2111751938231504</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2019247644226936</v>
+        <v>0.2019247644226933</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05629884226098074</v>
+        <v>0.0562988422609801</v>
       </c>
       <c r="O2" t="n">
-        <v>0.09312755473133882</v>
+        <v>0.09312755473133857</v>
       </c>
       <c r="P2" t="n">
-        <v>0.159834888058165</v>
+        <v>0.1598348880581646</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05100042374260131</v>
+        <v>0.0510004237426026</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3784082407648661</v>
+        <v>0.3784082407648657</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2464675491158412</v>
+        <v>0.2464675491158408</v>
       </c>
       <c r="T2" t="n">
-        <v>0.07342700820839894</v>
+        <v>0.07342700820839854</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2493126375245608</v>
+        <v>0.2493126375245605</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1949661150054366</v>
+        <v>0.1949661150054364</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1546326230614105</v>
+        <v>0.1546326230614101</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2243213804037634</v>
+        <v>0.2243213804037614</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1099101898845114</v>
+        <v>0.1099101898845105</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1004443812895306</v>
+        <v>0.100444381289533</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.3962860640833712</v>
+        <v>0.3962860640833702</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.08224233449697885</v>
+        <v>0.08224233449697878</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01822714417620031</v>
+        <v>0.01822714417620174</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02592687894248018</v>
+        <v>0.02592687894248015</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02384798919414169</v>
+        <v>0.02384798919414065</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02069641350690093</v>
+        <v>0.02069641350690088</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02094908921325352</v>
+        <v>0.02094908921325345</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02501350802495935</v>
+        <v>0.02501350802495859</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02384798919414169</v>
+        <v>0.02384798919414065</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02384798919414169</v>
+        <v>0.02384798919414065</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02324360513572304</v>
+        <v>0.0232436051357226</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02384798919414169</v>
+        <v>0.02384798919414065</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02384798919414169</v>
+        <v>0.02384798919414065</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02323187854570843</v>
+        <v>0.02323187854570842</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01949089395818993</v>
+        <v>0.01949089395819002</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02068826156071024</v>
+        <v>0.02068826156070764</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02039475782891081</v>
+        <v>0.02039475782890939</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0171225198408499</v>
+        <v>0.01712251984084914</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02384798919414169</v>
+        <v>0.02384798919414065</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02384798919414169</v>
+        <v>0.02384798919414065</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02384798919414169</v>
+        <v>0.02384798919414065</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02110405065834368</v>
+        <v>0.02110405065834564</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02081776213332576</v>
+        <v>0.02081776213332575</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02384909385057977</v>
+        <v>0.02384909385057881</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01763768145511821</v>
+        <v>0.01763768145511895</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02943584785120184</v>
+        <v>0.02943584785120193</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01812273409431941</v>
+        <v>0.01812273409431943</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02384798919414169</v>
+        <v>0.02384798919414065</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02880736448801996</v>
+        <v>0.02880736448801989</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06038727595041456</v>
+        <v>0.06038727595041257</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3666276629545311</v>
+        <v>0.3666276629545298</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3745687085183769</v>
+        <v>0.3745687085183751</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3403201988286195</v>
+        <v>0.3403201988286187</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3510033357696828</v>
+        <v>0.351003335769682</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07617540723130097</v>
+        <v>0.07617540723129933</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07852332769874833</v>
+        <v>0.07852332769874687</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1897980653087596</v>
+        <v>0.1897980653087579</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1041143150602609</v>
+        <v>0.1041143150602604</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1127631356685282</v>
+        <v>0.1127631356685267</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1123336978454335</v>
+        <v>0.1123336978454323</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1085704794011786</v>
+        <v>0.1085704794011773</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0558830863509635</v>
+        <v>0.05588308635096432</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0693067195818329</v>
+        <v>0.06930671958183159</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09362075926240541</v>
+        <v>0.09362075926240387</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05395187501818578</v>
+        <v>0.05395187501818417</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1732881797061072</v>
+        <v>0.173288179706106</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1251973469258615</v>
+        <v>0.1251973469258606</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06212610170971841</v>
+        <v>0.06212610170971697</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1262343482421251</v>
+        <v>0.1262343482421238</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1028409985935092</v>
+        <v>0.102840998593509</v>
       </c>
       <c r="W4" t="n">
-        <v>0.09172459475916818</v>
+        <v>0.09172459475916675</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1171253284837515</v>
+        <v>0.1171253284837486</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07542379302351289</v>
+        <v>0.07542379302350966</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.07197361694377863</v>
+        <v>0.07197361694377707</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1798044363737014</v>
+        <v>0.1798044363736997</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.06475955512624404</v>
+        <v>0.06475955512624276</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04200639945951109</v>
+        <v>0.04200639945950976</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04613402121359478</v>
+        <v>0.04613402121359366</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04405513146525612</v>
+        <v>0.04405513146525547</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04280560058617555</v>
+        <v>0.0428056005861742</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0441718510374727</v>
+        <v>0.04417185103747163</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04447994939287603</v>
+        <v>0.04447994939287429</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04405513146525612</v>
+        <v>0.04405513146525547</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04405513146525612</v>
+        <v>0.04405513146525547</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0430557103788409</v>
+        <v>0.04305571037884121</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04405513146525612</v>
+        <v>0.04405513146525547</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04405513146525612</v>
+        <v>0.04405513146525547</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04343902081682325</v>
+        <v>0.04343902081682201</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04246702141534713</v>
+        <v>0.04246702141534525</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04290344784626544</v>
+        <v>0.04290344784626354</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04279646918251943</v>
+        <v>0.04279646918251764</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04160377686042971</v>
+        <v>0.04160377686043012</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04405513146525612</v>
+        <v>0.04405513146525547</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04405513146525612</v>
+        <v>0.04405513146525547</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04405513146525612</v>
+        <v>0.04405513146525547</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04305499808991091</v>
+        <v>0.04305499808990934</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0393659689248293</v>
+        <v>0.03936596892482922</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04405553409955633</v>
+        <v>0.04405553409955506</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04179154721949746</v>
+        <v>0.04179154721949506</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04609184032980539</v>
+        <v>0.04609184032980348</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04196834321071058</v>
+        <v>0.04196834321070948</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04405513146525612</v>
+        <v>0.04405513146525547</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04528313602307545</v>
+        <v>0.04528313602307446</v>
       </c>
     </row>
     <row r="6">
@@ -938,82 +938,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03325861562782342</v>
+        <v>0.03325861562782328</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3394990026319388</v>
+        <v>0.3394990026319391</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3474400481957822</v>
+        <v>0.347440048195782</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3131915385060286</v>
+        <v>0.3131915385060287</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3238746754470912</v>
+        <v>0.3238746754470913</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04677421611541125</v>
+        <v>0.04677421611541105</v>
       </c>
       <c r="H6" t="n">
-        <v>0.051394667376157</v>
+        <v>0.0513946673761566</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1626694049861692</v>
+        <v>0.1626694049861687</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07518498262784427</v>
+        <v>0.0751849826278438</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08563447534593685</v>
+        <v>0.08563447534593674</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08520503752284184</v>
+        <v>0.08520503752284322</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08144181907858736</v>
+        <v>0.08144181907858737</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02875442602837227</v>
+        <v>0.02875442602837424</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03990552846594352</v>
+        <v>0.03990552846594343</v>
       </c>
       <c r="P6" t="n">
-        <v>0.06421956814651583</v>
+        <v>0.06421956814651568</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02682321469559452</v>
+        <v>0.02682321469559443</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1461595193835162</v>
+        <v>0.146159519383516</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09806868660326999</v>
+        <v>0.09806868660327013</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03499744138712714</v>
+        <v>0.0349974413871269</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09683315712623507</v>
+        <v>0.09683315712623494</v>
       </c>
       <c r="V6" t="n">
-        <v>0.07618005170687718</v>
+        <v>0.07618005170687711</v>
       </c>
       <c r="W6" t="n">
-        <v>0.06232340364327857</v>
+        <v>0.06232340364327842</v>
       </c>
       <c r="X6" t="n">
-        <v>0.08772413736786201</v>
+        <v>0.08772413736786085</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.04829513270092168</v>
+        <v>0.04829513270091963</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.04484495662118756</v>
+        <v>0.04484495662118754</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1526757760511111</v>
+        <v>0.152675776051111</v>
       </c>
       <c r="AB6" t="n">
         <v>0.0376308948036528</v>
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01487773913691993</v>
+        <v>0.01487773913691977</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01900536089100349</v>
+        <v>0.01900536089100351</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01692647114266494</v>
+        <v>0.01692647114266527</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01567694026358428</v>
+        <v>0.01567694026358423</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01704319071488139</v>
+        <v>0.01704319071488135</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01507875827698668</v>
+        <v>0.01507875827698631</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01692647114266494</v>
+        <v>0.01692647114266527</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01692647114266494</v>
+        <v>0.01692647114266527</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01412637794642454</v>
+        <v>0.01412637794642501</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01692647114266494</v>
+        <v>0.01692647114266527</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01692647114266494</v>
+        <v>0.01692647114266527</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01631036049423195</v>
+        <v>0.01631036049423189</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01533836109275599</v>
+        <v>0.01533836109275509</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0135022567303761</v>
+        <v>0.01350225673037541</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01339527806663006</v>
+        <v>0.01339527806662915</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01447511653783847</v>
+        <v>0.01447511653783998</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01692647114266494</v>
+        <v>0.01692647114266527</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01692647114266494</v>
+        <v>0.01692647114266527</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01692647114266494</v>
+        <v>0.01692647114266527</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01365380697402139</v>
+        <v>0.01365380697402104</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01270502203819749</v>
+        <v>0.01270502203819748</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01465434298366686</v>
+        <v>0.01465434298366683</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01239035610360796</v>
+        <v>0.01239035610360662</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01896318000721419</v>
+        <v>0.0189631800072133</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01483968288811941</v>
+        <v>0.01483968288811953</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01692647114266494</v>
+        <v>0.01692647114266527</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01815447570048431</v>
+        <v>0.01815447570048428</v>
       </c>
     </row>
   </sheetData>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01859351867518675</v>
+        <v>0.01859351867517729</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7444021348792502</v>
+        <v>0.7444021348792514</v>
       </c>
       <c r="D2" t="n">
-        <v>0.174184093191552</v>
+        <v>0.174184093191542</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5342551874382244</v>
+        <v>0.534255187438224</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9086805460849776</v>
+        <v>0.9086805460849777</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06185793748345153</v>
+        <v>0.06185793748344415</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1366757022845526</v>
+        <v>0.1366757022845433</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1605986616224545</v>
+        <v>0.1605986616224445</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1620044272582387</v>
+        <v>0.162004427258235</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1997101179750778</v>
+        <v>0.199710117975068</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2754100943498829</v>
+        <v>0.2754100943498692</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2401585836769642</v>
+        <v>0.2401585836769641</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04339606984742363</v>
+        <v>0.04339606984742622</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1134035342781016</v>
+        <v>0.1134035342780895</v>
       </c>
       <c r="P2" t="n">
-        <v>0.170311218774456</v>
+        <v>0.1703112187744549</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02666825502691581</v>
+        <v>0.02666825502690614</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1818340652720002</v>
+        <v>0.1818340652719915</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2563661958188594</v>
+        <v>0.2563661958188508</v>
       </c>
       <c r="T2" t="n">
-        <v>0.08689286244456469</v>
+        <v>0.08689286244455871</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1463918670984816</v>
+        <v>0.1463918670984717</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1387122827658923</v>
+        <v>0.1387122827658924</v>
       </c>
       <c r="W2" t="n">
-        <v>0.09947427381947774</v>
+        <v>0.09947427381947285</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2462336726252612</v>
+        <v>0.2462336726252512</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05362200484680045</v>
+        <v>0.05362200484678936</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.04189917432261066</v>
+        <v>0.04189917432260555</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1330453241391926</v>
+        <v>0.1330453241391827</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.09263245867659475</v>
+        <v>0.09263245867659471</v>
       </c>
     </row>
     <row r="3">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01671183760161947</v>
+        <v>0.01671183760161167</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02422772394630933</v>
+        <v>0.02422772394630935</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02216929157746832</v>
+        <v>0.0221692915774708</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01894999356867798</v>
+        <v>0.018949993568678</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01997717397982316</v>
+        <v>0.01997717397982313</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02330093021131296</v>
+        <v>0.02330093021131155</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02216929157746832</v>
+        <v>0.0221692915774708</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02216929157746832</v>
+        <v>0.0221692915774708</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0217213387870371</v>
+        <v>0.02172133878703204</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02216929157746832</v>
+        <v>0.0221692915774708</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02216929157746832</v>
+        <v>0.0221692915774708</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02205076804616685</v>
+        <v>0.02205076804616694</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01793885173383715</v>
+        <v>0.01793885173383122</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01910141333476712</v>
+        <v>0.01910141333476284</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01881644139500176</v>
+        <v>0.01881644139499156</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01563932333527893</v>
+        <v>0.01563932333527627</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02216929157746832</v>
+        <v>0.0221692915774708</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02216929157746832</v>
+        <v>0.0221692915774708</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02216929157746832</v>
+        <v>0.0221692915774708</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01950636487930544</v>
+        <v>0.01950636487930169</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01951050377877866</v>
+        <v>0.01951050377877863</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02217036412278769</v>
+        <v>0.02217036412278457</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01613950983582543</v>
+        <v>0.01613950983581437</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02759685461068568</v>
+        <v>0.02759685461068278</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01661046259223569</v>
+        <v>0.01661046259223109</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02216929157746832</v>
+        <v>0.0221692915774708</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02740869109531081</v>
+        <v>0.0274086910953108</v>
       </c>
     </row>
     <row r="4">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03556008562036354</v>
+        <v>0.03556008562035251</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3014169612933887</v>
+        <v>0.301416961293394</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09227102299480897</v>
+        <v>0.09227102299479545</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2233135617000666</v>
+        <v>0.2233135617000701</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3615211979139165</v>
+        <v>0.3615211979139184</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05132945823952098</v>
+        <v>0.05132945823950704</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07859965495497212</v>
+        <v>0.07859965495496062</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08731929271606557</v>
+        <v>0.08731929271605476</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08734711256398532</v>
+        <v>0.08734711256398831</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1015749592866891</v>
+        <v>0.1015749592866775</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1291667117612963</v>
+        <v>0.1291667117612896</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1162426269692355</v>
+        <v>0.1162426269692371</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04460032427637715</v>
+        <v>0.04460032427637689</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0701172229922129</v>
+        <v>0.07011722299220437</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09085940574735944</v>
+        <v>0.09085940574735792</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03850323220222782</v>
+        <v>0.03850323220221644</v>
       </c>
       <c r="R4" t="n">
-        <v>0.09505934798762557</v>
+        <v>0.09505934798761523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1222254343714906</v>
+        <v>0.1222254343714821</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0604543944129084</v>
+        <v>0.06045439441290588</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08214108293668107</v>
+        <v>0.08214108293667002</v>
       </c>
       <c r="V4" t="n">
-        <v>0.07726607083615947</v>
+        <v>0.07726607083615959</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06504017112068106</v>
+        <v>0.06504017112067069</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1185322486495199</v>
+        <v>0.1185322486495097</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.04832755750466338</v>
+        <v>0.04832755750465524</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0440547234350199</v>
+        <v>0.0440547234350146</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0772764247510378</v>
+        <v>0.07727642475103101</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.06225320537524637</v>
+        <v>0.06225320537524852</v>
       </c>
     </row>
     <row r="5">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03487423496485561</v>
+        <v>0.03487423496485389</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03892184522323118</v>
+        <v>0.0389218452232321</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0368634128543931</v>
+        <v>0.03686341285439347</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03549086955371143</v>
+        <v>0.03549086955370988</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03759925446345706</v>
+        <v>0.03759925446346128</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03727588184806016</v>
+        <v>0.03727588184805758</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0368634128543931</v>
+        <v>0.03686341285439347</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0368634128543931</v>
+        <v>0.03686341285439347</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03621557410342639</v>
+        <v>0.03621557410342578</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0368634128543931</v>
+        <v>0.03686341285439347</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0368634128543931</v>
+        <v>0.03686341285439347</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03674488932309053</v>
+        <v>0.03674488932308935</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03532146720772204</v>
+        <v>0.03532146720771966</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03574520725977803</v>
+        <v>0.03574520725977219</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03564133833404277</v>
+        <v>0.03564133833403417</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03448331610887279</v>
+        <v>0.03448331610887187</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0368634128543931</v>
+        <v>0.03686341285439347</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0368634128543931</v>
+        <v>0.03686341285439347</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0368634128543931</v>
+        <v>0.03686341285439347</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03589280734257541</v>
+        <v>0.03589280734257463</v>
       </c>
       <c r="V5" t="n">
-        <v>0.033818422133315</v>
+        <v>0.03381842213331514</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03686380378456869</v>
+        <v>0.03686380378456584</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03466562821483572</v>
+        <v>0.03466562821483185</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0388416958463406</v>
+        <v>0.03884169584633678</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03483728496433729</v>
+        <v>0.03483728496433923</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0368634128543931</v>
+        <v>0.03686341285439347</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0384799079880135</v>
+        <v>0.03847990798801826</v>
       </c>
     </row>
     <row r="6">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01421585164240194</v>
+        <v>0.01421585164239137</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2800727273154334</v>
+        <v>0.2800727273154337</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07092678901684761</v>
+        <v>0.07092678901683806</v>
       </c>
       <c r="E6" t="n">
         <v>0.2019693277221098</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3401769639359589</v>
+        <v>0.3401769639359586</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02770854779444988</v>
+        <v>0.02770854779443809</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05725542097700983</v>
+        <v>0.05725542097699999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06597505873810375</v>
+        <v>0.06597505873809276</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06400283164883022</v>
+        <v>0.06400283164882768</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08023072530872652</v>
+        <v>0.08023072530871625</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1078224777833374</v>
+        <v>0.1078224777833346</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09489839299127648</v>
+        <v>0.09489839299127628</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02325609029842098</v>
+        <v>0.02325609029841597</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04649631254714306</v>
+        <v>0.04649631254713446</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0672384953022877</v>
+        <v>0.06723849530228836</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01715899822426576</v>
+        <v>0.01715899822425565</v>
       </c>
       <c r="R6" t="n">
-        <v>0.07371511400966374</v>
+        <v>0.0737151140096501</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1008812003935312</v>
+        <v>0.1008812003935197</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03911016043494864</v>
+        <v>0.03911016043494442</v>
       </c>
       <c r="U6" t="n">
-        <v>0.05852017249160987</v>
+        <v>0.05852017249159992</v>
       </c>
       <c r="V6" t="n">
-        <v>0.05508305049624392</v>
+        <v>0.05508305049624402</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04141926067560964</v>
+        <v>0.04141926067560045</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0949113382044489</v>
+        <v>0.09491133820443913</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02698332352670356</v>
+        <v>0.0269833235266932</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02271048945705671</v>
+        <v>0.02271048945705417</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.05593219077307515</v>
+        <v>0.05593219077307175</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.04090897139728812</v>
+        <v>0.04090897139728811</v>
       </c>
     </row>
     <row r="7">
@@ -1710,82 +1710,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01353000098689542</v>
+        <v>0.0135300009868906</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01757761124527168</v>
+        <v>0.0175776112452717</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01551917887643371</v>
+        <v>0.01551917887643226</v>
       </c>
       <c r="E7" t="n">
         <v>0.01414663557574958</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01625502048550077</v>
+        <v>0.01625502048550074</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01365497140299136</v>
+        <v>0.01365497140298686</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01551917887643371</v>
+        <v>0.01551917887643226</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01551917887643371</v>
+        <v>0.01551917887643226</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01287129318827093</v>
+        <v>0.01287129318826695</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01551917887643371</v>
+        <v>0.01551917887643226</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01551917887643371</v>
+        <v>0.01551917887643226</v>
       </c>
       <c r="M7" t="n">
-        <v>0.015400655345129</v>
+        <v>0.01540065534512878</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01397723322976569</v>
+        <v>0.01397723322975826</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01212429681470659</v>
+        <v>0.01212429681470146</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01202042788897304</v>
+        <v>0.01202042788896476</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01313908213091476</v>
+        <v>0.01313908213091102</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01551917887643371</v>
+        <v>0.01551917887643226</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01551917887643371</v>
+        <v>0.01551917887643226</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01551917887643371</v>
+        <v>0.01551917887643226</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01227189689750506</v>
+        <v>0.01227189689750531</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01163540179339958</v>
+        <v>0.01163540179339957</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01324289333949914</v>
+        <v>0.01324289333949595</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01104471776976903</v>
+        <v>0.0110447177697622</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01749746186838098</v>
+        <v>0.01749746186837504</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01349305098638056</v>
+        <v>0.01349305098637815</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01551917887643371</v>
+        <v>0.01551917887643226</v>
       </c>
       <c r="AB7" t="n">
         <v>0.01713567401005753</v>
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05828800964198743</v>
+        <v>0.05828800964199266</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8788018873705954</v>
+        <v>0.8788018873705986</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5852328555868644</v>
+        <v>0.585232855586867</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8050458435948934</v>
+        <v>0.8050458435948964</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9296619065277388</v>
+        <v>0.9296619065277404</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1066807566445088</v>
+        <v>0.1066807566445113</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1536281517894763</v>
+        <v>0.1536281517894796</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4942922304908252</v>
+        <v>0.4942922304908276</v>
       </c>
       <c r="J2" t="n">
-        <v>0.193302410024368</v>
+        <v>0.1933024100243634</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2467048757582311</v>
+        <v>0.2467048757582326</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2588955734561557</v>
+        <v>0.2588955734561619</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2021988024448959</v>
+        <v>0.2021988024448962</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05466551352515377</v>
+        <v>0.05466551352515727</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1124944158175168</v>
+        <v>0.1124944158175209</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1589452000785192</v>
+        <v>0.1589452000785211</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05106899521430117</v>
+        <v>0.05106899521430396</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3632729058185625</v>
+        <v>0.3632729058185654</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3019693712364602</v>
+        <v>0.3019693712364635</v>
       </c>
       <c r="T2" t="n">
-        <v>0.07100543413058759</v>
+        <v>0.07100543413059091</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2277526112414542</v>
+        <v>0.2277526112414572</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2102437252263821</v>
+        <v>0.2102437252263814</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1334885146704018</v>
+        <v>0.1334885146704001</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2317569693055432</v>
+        <v>0.2317569693055456</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1086209035763562</v>
+        <v>0.1086209035763586</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.09677309250826974</v>
+        <v>0.09677309250827229</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.3257677565105372</v>
+        <v>0.3257677565105402</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.08044364752018332</v>
+        <v>0.08044364752018669</v>
       </c>
     </row>
     <row r="3">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01818238590984887</v>
+        <v>0.01818238590984306</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0259311235428318</v>
+        <v>0.02593112354282908</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02385207484191935</v>
+        <v>0.02385207484191604</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02068498756207125</v>
+        <v>0.02068498756207129</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02121238808795054</v>
+        <v>0.02121238808795059</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02502772177651756</v>
+        <v>0.02502772177651346</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02385207484191935</v>
+        <v>0.02385207484191604</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02385207484191935</v>
+        <v>0.02385207484191604</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0232911968779589</v>
+        <v>0.02329119687795758</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02385207484191935</v>
+        <v>0.02385207484191604</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02385207484191935</v>
+        <v>0.02385207484191604</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02330233764744289</v>
+        <v>0.02330233764744292</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01945711740109466</v>
+        <v>0.01945711740108869</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02066488986623055</v>
+        <v>0.02066488986622216</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0203688356511942</v>
+        <v>0.02036883565118875</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01706816263058035</v>
+        <v>0.017068162630576</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02385207484191935</v>
+        <v>0.02385207484191604</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02385207484191935</v>
+        <v>0.02385207484191604</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02385207484191935</v>
+        <v>0.02385207484191604</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02108426040696159</v>
+        <v>0.02108426040695651</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02090650042182006</v>
+        <v>0.02090650042182075</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02385318909751676</v>
+        <v>0.0238531890975153</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0175878008865945</v>
+        <v>0.0175878008865928</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02948843658511132</v>
+        <v>0.02948843658510545</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01807706852718959</v>
+        <v>0.01807706852718586</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02385207484191935</v>
+        <v>0.02385207484191604</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02892622260904145</v>
+        <v>0.02892622260904143</v>
       </c>
     </row>
     <row r="4">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0556440658916271</v>
+        <v>0.05564406589162885</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3560329992261609</v>
+        <v>0.3560329992261593</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2477092745397507</v>
+        <v>0.2477092745397523</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3277343794997168</v>
+        <v>0.327734379499718</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3746138918162933</v>
+        <v>0.3746138918162929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07328265391772093</v>
+        <v>0.0732826539177234</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09039442816391506</v>
+        <v>0.09039442816391745</v>
       </c>
       <c r="I4" t="n">
-        <v>0.214562484570982</v>
+        <v>0.2145624845709802</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1043881426870489</v>
+        <v>0.1043881426870437</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1243198010884519</v>
+        <v>0.1243198010884537</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1287631672489453</v>
+        <v>0.1287631672489434</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1077484955400152</v>
+        <v>0.1077484955400148</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05432370859453992</v>
+        <v>0.05432370859454109</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07540166441885063</v>
+        <v>0.07540166441885246</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09233242982933866</v>
+        <v>0.09233242982933978</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05301281990268408</v>
+        <v>0.05301281990268524</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1668074792345264</v>
+        <v>0.1668074792345275</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1444630607417967</v>
+        <v>0.1444630607417979</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06027941778218508</v>
+        <v>0.06027941778218641</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1174119232208117</v>
+        <v>0.1174119232208146</v>
       </c>
       <c r="V4" t="n">
         <v>0.1094051767895804</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0830537669255723</v>
+        <v>0.08305376692557187</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1188714647136287</v>
+        <v>0.1188714647136306</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07398981469202395</v>
+        <v>0.07398981469202598</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06967142668172824</v>
+        <v>0.06967142668172999</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1531372927194478</v>
+        <v>0.15313729271945</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.06318042069145499</v>
+        <v>0.06318042069145458</v>
       </c>
     </row>
     <row r="5">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04102603698527693</v>
+        <v>0.04102603698527418</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04517162072508105</v>
+        <v>0.04517162072507511</v>
       </c>
       <c r="D5" t="n">
-        <v>0.043092572024169</v>
+        <v>0.04309257202416134</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0418440579059405</v>
+        <v>0.04184405790593976</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04349470989781767</v>
+        <v>0.04349470989781686</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04352108152668381</v>
+        <v>0.04352108152668066</v>
       </c>
       <c r="H5" t="n">
-        <v>0.043092572024169</v>
+        <v>0.04309257202416134</v>
       </c>
       <c r="I5" t="n">
-        <v>0.043092572024169</v>
+        <v>0.04309257202416134</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04242105186763931</v>
+        <v>0.04242105186763559</v>
       </c>
       <c r="K5" t="n">
-        <v>0.043092572024169</v>
+        <v>0.04309257202416134</v>
       </c>
       <c r="L5" t="n">
-        <v>0.043092572024169</v>
+        <v>0.04309257202416134</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04254283482969257</v>
+        <v>0.04254283482969247</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04149066164518021</v>
+        <v>0.04149066164517784</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0419308805263441</v>
+        <v>0.04193088052633877</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04182297224140972</v>
+        <v>0.0418229722414019</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04061991568385093</v>
+        <v>0.04061991568385125</v>
       </c>
       <c r="R5" t="n">
-        <v>0.043092572024169</v>
+        <v>0.04309257202416134</v>
       </c>
       <c r="S5" t="n">
-        <v>0.043092572024169</v>
+        <v>0.04309257202416134</v>
       </c>
       <c r="T5" t="n">
-        <v>0.043092572024169</v>
+        <v>0.04309257202416134</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04208373616394179</v>
+        <v>0.04208373616393895</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04039398165826118</v>
+        <v>0.04039398165826161</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04309297815724498</v>
+        <v>0.04309297815724596</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04080931772627341</v>
+        <v>0.04080931772626903</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04514695969405628</v>
+        <v>0.04514695969405318</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04098765003599846</v>
+        <v>0.04098765003599302</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.043092572024169</v>
+        <v>0.04309257202416134</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04440292425948873</v>
+        <v>0.04440292425948832</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02940550092331326</v>
+        <v>0.02940550092331417</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3297944342578473</v>
+        <v>0.3297944342578474</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2214707095714357</v>
+        <v>0.2214707095714356</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3014958145314033</v>
+        <v>0.3014958145314043</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3483753268479791</v>
+        <v>0.3483753268479796</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04476821361666024</v>
+        <v>0.04476821361666179</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06415586319560111</v>
+        <v>0.06415586319560131</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1883239196026669</v>
+        <v>0.1883239196026648</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07606131606905313</v>
+        <v>0.0760613160690496</v>
       </c>
       <c r="K6" t="n">
-        <v>0.09808123612013747</v>
+        <v>0.09808123612013814</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1025246022806328</v>
+        <v>0.1025246022806285</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08150993057170086</v>
+        <v>0.08150993057170074</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02808514362622508</v>
+        <v>0.02808514362622532</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04688722411778868</v>
+        <v>0.04688722411779151</v>
       </c>
       <c r="P6" t="n">
-        <v>0.06381798952827579</v>
+        <v>0.06381798952827919</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02677425493436931</v>
+        <v>0.0267742549343689</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1405689142662116</v>
+        <v>0.1405689142662115</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1182244957734824</v>
+        <v>0.118224495773483</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03404085281387251</v>
+        <v>0.03404085281387085</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08889748291975218</v>
+        <v>0.08889748291975431</v>
       </c>
       <c r="V6" t="n">
-        <v>0.08173381647054602</v>
+        <v>0.08173381647054503</v>
       </c>
       <c r="W6" t="n">
-        <v>0.05453932662451019</v>
+        <v>0.05453932662451069</v>
       </c>
       <c r="X6" t="n">
-        <v>0.09035702441256661</v>
+        <v>0.09035702441256853</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.04775124972371006</v>
+        <v>0.04775124972371029</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.04343286171341339</v>
+        <v>0.04343286171341507</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1268987277511342</v>
+        <v>0.1268987277511346</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03694185572314052</v>
+        <v>0.03694185572314113</v>
       </c>
     </row>
     <row r="7">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01478747201696211</v>
+        <v>0.01478747201695661</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01893305575676688</v>
+        <v>0.01893305575675805</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01685400705585714</v>
+        <v>0.01685400705585071</v>
       </c>
       <c r="E7" t="n">
         <v>0.01560549293762638</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01725614492950365</v>
+        <v>0.01725614492950368</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01500664122562305</v>
+        <v>0.01500664122561994</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01685400705585714</v>
+        <v>0.01685400705585071</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01685400705585714</v>
+        <v>0.01685400705585071</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01409422524964534</v>
+        <v>0.01409422524964141</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01685400705585714</v>
+        <v>0.01685400705585071</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01685400705585714</v>
+        <v>0.01685400705585071</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01630426986137921</v>
+        <v>0.01630426986137923</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01525209667686746</v>
+        <v>0.01525209667686261</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01341644022528332</v>
+        <v>0.01341644022527812</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01330853194034885</v>
+        <v>0.01330853194034106</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01438135071553823</v>
+        <v>0.01438135071553376</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01685400705585714</v>
+        <v>0.01685400705585071</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01685400705585714</v>
+        <v>0.01685400705585071</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01685400705585714</v>
+        <v>0.01685400705585071</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01356929586288005</v>
+        <v>0.01356929586287873</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01272262133922709</v>
+        <v>0.01272262133922766</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01457853785618203</v>
+        <v>0.01457853785618532</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01229487742521161</v>
+        <v>0.0122948774252084</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01890839472574346</v>
+        <v>0.01890839472574153</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01474908506768479</v>
+        <v>0.01474908506767906</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01685400705585714</v>
+        <v>0.01685400705585071</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01816435929117508</v>
+        <v>0.0181643592911751</v>
       </c>
     </row>
   </sheetData>
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05148433470065619</v>
+        <v>0.05148433470065525</v>
       </c>
       <c r="C2" t="n">
         <v>0.7121146984406758</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3725557716485029</v>
+        <v>0.3725557716485022</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5891236513563328</v>
+        <v>0.5891236513563322</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8710315232091677</v>
+        <v>0.8710315232091685</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09969641816479702</v>
+        <v>0.0996964181647961</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1400605244295557</v>
+        <v>0.1400605244295546</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2543213930139188</v>
+        <v>0.2543213930139177</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1699228451420161</v>
+        <v>0.169922845142017</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2056087053930679</v>
+        <v>0.2056087053930668</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2449167741711784</v>
+        <v>0.2449167741711765</v>
       </c>
       <c r="M2" t="n">
         <v>0.1593258235744331</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04838133337389926</v>
+        <v>0.0483813333738981</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1241650849968189</v>
+        <v>0.1241650849968176</v>
       </c>
       <c r="P2" t="n">
-        <v>0.150412501087557</v>
+        <v>0.1504125010875555</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05333284298493903</v>
+        <v>0.05333284298493803</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3546587886720744</v>
+        <v>0.3546587886720736</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2358378174175597</v>
+        <v>0.2358378174175581</v>
       </c>
       <c r="T2" t="n">
-        <v>0.08735149089290054</v>
+        <v>0.08735149089289987</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1533439752579776</v>
+        <v>0.1533439752579763</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1951236781737079</v>
+        <v>0.1951236781737087</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1259607028099906</v>
+        <v>0.1259607028099894</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2372310063354524</v>
+        <v>0.2372310063354513</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09933639333531055</v>
+        <v>0.09933639333530961</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.08656383861495896</v>
+        <v>0.08656383861495812</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2314106385946016</v>
+        <v>0.2314106385946001</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.09355659716817345</v>
+        <v>0.09355659716817351</v>
       </c>
     </row>
     <row r="3">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01764608812471858</v>
+        <v>0.01764608812471809</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02504405124434068</v>
+        <v>0.02504405124434066</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02322788726395368</v>
+        <v>0.02322788726395332</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01986228103325844</v>
+        <v>0.01986228103325846</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02061887080069118</v>
+        <v>0.02061887080069119</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0243853096774525</v>
+        <v>0.02438530967745206</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02322788726395368</v>
+        <v>0.02322788726395332</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02322788726395368</v>
+        <v>0.02322788726395332</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02272133510820182</v>
+        <v>0.02272133510820311</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02322788726395368</v>
+        <v>0.02322788726395332</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02322788726395368</v>
+        <v>0.02322788726395332</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02271198161082684</v>
+        <v>0.02271198161082685</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0189010591161964</v>
+        <v>0.01890105911619609</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02009010906000453</v>
+        <v>0.02009010906000601</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01979864418734842</v>
+        <v>0.01979864418734802</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01654913719575104</v>
+        <v>0.01654913719575242</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02322788726395368</v>
+        <v>0.02322788726395332</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02322788726395368</v>
+        <v>0.02322788726395332</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02322788726395368</v>
+        <v>0.02322788726395332</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02050482064994401</v>
+        <v>0.02050482064994834</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02044559509977046</v>
+        <v>0.02044559509977122</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02322898424661666</v>
+        <v>0.02322898424661751</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01706072017756673</v>
+        <v>0.01706072017756725</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02878002697468643</v>
+        <v>0.02878002697468457</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01754240334009296</v>
+        <v>0.01754240334009264</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02322788726395368</v>
+        <v>0.02322788726395332</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02841659473386857</v>
+        <v>0.02841659473386852</v>
       </c>
     </row>
     <row r="4">
@@ -2814,85 +2814,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0511414313623294</v>
+        <v>0.05114143136232729</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2930876349681854</v>
+        <v>0.2930876349681862</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1681681999186561</v>
+        <v>0.1681681999186549</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2468545987473506</v>
+        <v>0.2468545987473509</v>
       </c>
       <c r="F4" t="n">
-        <v>0.351193368553411</v>
+        <v>0.3511933685534123</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06871416965014095</v>
+        <v>0.06871416965013991</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08342641240437908</v>
+        <v>0.08342641240437772</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1250731572845207</v>
+        <v>0.1250731572845195</v>
       </c>
       <c r="J4" t="n">
-        <v>0.09395846915563776</v>
+        <v>0.09395846915563921</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1073179546599778</v>
+        <v>0.1073179546599767</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1216452841509507</v>
+        <v>0.1216452841509499</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09012052361749245</v>
+        <v>0.09012052361749295</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05001042381600698</v>
+        <v>0.0500104238160055</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07763271138482063</v>
+        <v>0.07763271138481914</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08719958633717392</v>
+        <v>0.08719958633717245</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05181519092566924</v>
+        <v>0.05181519092566829</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1616449597807327</v>
+        <v>0.1616449597807313</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1183361110247504</v>
+        <v>0.118336111024749</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06421458862098933</v>
+        <v>0.06421458862098828</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08826807424918462</v>
+        <v>0.08826807424918333</v>
       </c>
       <c r="V4" t="n">
-        <v>0.102493291337885</v>
+        <v>0.1024932913378879</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07828719299251287</v>
+        <v>0.07828719299251159</v>
       </c>
       <c r="X4" t="n">
         <v>0.1188439120256707</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0685829448274177</v>
+        <v>0.06858294482741648</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06392749861476023</v>
+        <v>0.06392749861475863</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1167224563303406</v>
+        <v>0.1167224563303393</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0660683112017568</v>
+        <v>0.0660683112017573</v>
       </c>
     </row>
     <row r="5">
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03880778783415177</v>
+        <v>0.03880778783415086</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04265845205599546</v>
+        <v>0.0426584520559958</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04084228807560832</v>
+        <v>0.04084228807560972</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0393655138690917</v>
+        <v>0.03936551386909212</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04122794280005981</v>
+        <v>0.04122794280006036</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04126415495418807</v>
+        <v>0.04126415495419031</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04084228807560832</v>
+        <v>0.04084228807560972</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04084228807560832</v>
+        <v>0.04084228807560972</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04030524727571312</v>
+        <v>0.04030524727571444</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04084228807560832</v>
+        <v>0.04084228807560972</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04084228807560832</v>
+        <v>0.04084228807560972</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04032638242248276</v>
+        <v>0.04032638242248326</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03926521002393192</v>
+        <v>0.03926521002393404</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03969860476592127</v>
+        <v>0.03969860476592258</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03959236924239086</v>
+        <v>0.03959236924238962</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03840796210159148</v>
+        <v>0.03840796210159111</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04084228807560832</v>
+        <v>0.04084228807560972</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04084228807560832</v>
+        <v>0.04084228807560972</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04084228807560832</v>
+        <v>0.04084228807560972</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03984976227066444</v>
+        <v>0.03984976227066519</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03882518123104581</v>
+        <v>0.03882518123104552</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04084268791290743</v>
+        <v>0.04084268791290923</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03859442809115275</v>
+        <v>0.03859442809115492</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04286597780365405</v>
+        <v>0.04286597780365289</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03876999594768411</v>
+        <v>0.03876999594768387</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04084228807560832</v>
+        <v>0.04084228807560972</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0423255452269803</v>
+        <v>0.04232554522698071</v>
       </c>
     </row>
     <row r="6">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02667475328471183</v>
+        <v>0.02667475328470927</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2686209568905672</v>
+        <v>0.2686209568905671</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1437015218410377</v>
+        <v>0.143701521841036</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2223879206697328</v>
+        <v>0.2223879206697325</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3267266904757924</v>
+        <v>0.3267266904757928</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04196958756434627</v>
+        <v>0.04196958756434449</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05895973432676154</v>
+        <v>0.05895973432675984</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1006064792069024</v>
+        <v>0.1006064792069009</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06732137124968621</v>
+        <v>0.06732137124968746</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08285127658235994</v>
+        <v>0.08285127658235839</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0971786060733334</v>
+        <v>0.09717860607333177</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06565384553987463</v>
+        <v>0.06565384553987469</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02554374573838895</v>
+        <v>0.02554374573838733</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0508881292990257</v>
+        <v>0.05088812929902384</v>
       </c>
       <c r="P6" t="n">
-        <v>0.06045500425137902</v>
+        <v>0.06045500425137695</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02734851284805127</v>
+        <v>0.02734851284804998</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1371782817031151</v>
+        <v>0.137178281703113</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09386943294713246</v>
+        <v>0.09386943294713083</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03974791054337166</v>
+        <v>0.03974791054337019</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0615234921633895</v>
+        <v>0.06152349216338784</v>
       </c>
       <c r="V6" t="n">
-        <v>0.07605700699200081</v>
+        <v>0.07605700699200163</v>
       </c>
       <c r="W6" t="n">
-        <v>0.05154261090671784</v>
+        <v>0.05154261090671611</v>
       </c>
       <c r="X6" t="n">
-        <v>0.09209932993987778</v>
+        <v>0.0920993299398753</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.04411626674980013</v>
+        <v>0.04411626674979878</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03946082053714175</v>
+        <v>0.03946082053714033</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0922557782527221</v>
+        <v>0.09225577825272036</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.04160163312413927</v>
+        <v>0.04160163312413928</v>
       </c>
     </row>
     <row r="7">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01434110975653427</v>
+        <v>0.01434110975653258</v>
       </c>
       <c r="C7" t="n">
         <v>0.01819177397837756</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01637560999799021</v>
+        <v>0.0163756099979916</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01489883579147377</v>
+        <v>0.01489883579147376</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01676126472244205</v>
+        <v>0.01676126472244207</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01451957286839314</v>
+        <v>0.01451957286839478</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01637560999799021</v>
+        <v>0.0163756099979916</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01637560999799021</v>
+        <v>0.0163756099979916</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01366814936976171</v>
+        <v>0.01366814936976162</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01637560999799021</v>
+        <v>0.0163756099979916</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01637560999799021</v>
+        <v>0.0163756099979916</v>
       </c>
       <c r="M7" t="n">
         <v>0.01585970434486517</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01479853194631418</v>
+        <v>0.01479853194631597</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0129540226801263</v>
+        <v>0.01295402268012686</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01284778715659583</v>
+        <v>0.0128477871565942</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0139412840239736</v>
+        <v>0.01394128402397261</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01637560999799021</v>
+        <v>0.0163756099979916</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01637560999799021</v>
+        <v>0.0163756099979916</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01637560999799021</v>
+        <v>0.0163756099979916</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01310518018486942</v>
+        <v>0.01310518018486961</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01238889688516163</v>
+        <v>0.01238889688516194</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01409810582711249</v>
+        <v>0.01409810582711381</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01184984600535773</v>
+        <v>0.0118498460053594</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01839929972603621</v>
+        <v>0.01839929972603459</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01430331787006637</v>
+        <v>0.01430331787006562</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01637560999799021</v>
+        <v>0.0163756099979916</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01785886714936248</v>
+        <v>0.01785886714936247</v>
       </c>
     </row>
   </sheetData>
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04818417852996115</v>
+        <v>0.04818417852995754</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7306228760971014</v>
+        <v>0.730622876097101</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2974160636693109</v>
+        <v>0.2974160636693082</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5359262888774483</v>
+        <v>0.535926288877448</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7697105271678915</v>
+        <v>0.7697105271678923</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09067170350975561</v>
+        <v>0.09067170350975255</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1193445647936367</v>
+        <v>0.1193445647936331</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1726355800559171</v>
+        <v>0.1726355800559133</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1611924848648366</v>
+        <v>0.161192484864835</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1684437350626734</v>
+        <v>0.1684437350626703</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2422676868965449</v>
+        <v>0.2422676868965429</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1883657204553054</v>
+        <v>0.1883657204553063</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04339106539586838</v>
+        <v>0.0433910653958649</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1084764024615652</v>
+        <v>0.1084764024615616</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1249259202317789</v>
+        <v>0.1249259202317772</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05724077987837432</v>
+        <v>0.05724077987837096</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2785118603997877</v>
+        <v>0.2785118603997841</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2112124418977341</v>
+        <v>0.2112124418977317</v>
       </c>
       <c r="T2" t="n">
-        <v>0.09430330079544524</v>
+        <v>0.09430330079544197</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1095607764816116</v>
+        <v>0.1095607764816081</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1684400982723425</v>
+        <v>0.1684400982723423</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1068529912716899</v>
+        <v>0.1068529912716862</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2428619163196614</v>
+        <v>0.2428619163196593</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0814026881557747</v>
+        <v>0.08140268815577363</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.06872229508810769</v>
+        <v>0.06872229508810629</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1862616907419798</v>
+        <v>0.186261690741976</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.09188311906656432</v>
+        <v>0.09188311906656436</v>
       </c>
     </row>
     <row r="3">
@@ -3410,82 +3410,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01714711089353116</v>
+        <v>0.01714711089353008</v>
       </c>
       <c r="C3" t="n">
         <v>0.02463552778548767</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02266480398128433</v>
+        <v>0.02266480398128114</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01935284064470453</v>
+        <v>0.01935284064470454</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01987841780176574</v>
+        <v>0.01987841780176573</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02380893358739524</v>
+        <v>0.02380893358739172</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02266480398128433</v>
+        <v>0.02266480398128114</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02266480398128433</v>
+        <v>0.02266480398128114</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02219895258960113</v>
+        <v>0.02219895258960097</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02266480398128433</v>
+        <v>0.02266480398128114</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02266480398128433</v>
+        <v>0.02266480398128114</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02234337554961615</v>
+        <v>0.02234337554961693</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01838766874813148</v>
+        <v>0.01838766874813071</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01956306264753096</v>
+        <v>0.01956306264752665</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01927494520133601</v>
+        <v>0.01927494520133179</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01606275826682991</v>
+        <v>0.01606275826682884</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02266480398128433</v>
+        <v>0.02266480398128114</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02266480398128433</v>
+        <v>0.02266480398128114</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02266480398128433</v>
+        <v>0.02266480398128114</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01997441053395783</v>
+        <v>0.01997441053395469</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01997772561832152</v>
+        <v>0.0199777256183213</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02266588836526652</v>
+        <v>0.02266588836526393</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01656846580164357</v>
+        <v>0.01656846580164283</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02815557188355934</v>
+        <v>0.02815557188355731</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01704461691172602</v>
+        <v>0.01704461691172263</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02266480398128433</v>
+        <v>0.02266480398128114</v>
       </c>
       <c r="AB3" t="n">
         <v>0.02790099310864059</v>
@@ -3498,13 +3498,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04796929112482747</v>
+        <v>0.04796929112482522</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2979626009072522</v>
+        <v>0.2979626009072516</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1388113866295654</v>
+        <v>0.1388113866295632</v>
       </c>
       <c r="E4" t="n">
         <v>0.2255079104948997</v>
@@ -3513,70 +3513,70 @@
         <v>0.3121466693549417</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06345549506625496</v>
+        <v>0.06345549506625325</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0739064163104932</v>
+        <v>0.07390641631049101</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09333036559889939</v>
+        <v>0.09333036559889719</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08879050883020025</v>
+        <v>0.08879050883019915</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09180248732199142</v>
+        <v>0.09180248732198917</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1187104508808281</v>
+        <v>0.1187104508808268</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09885954551911591</v>
+        <v>0.09885954551911627</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04622225767102651</v>
+        <v>0.04622225767102439</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06994509876085872</v>
+        <v>0.06994509876085651</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07594075482811155</v>
+        <v>0.07594075482811027</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05127031596834166</v>
+        <v>0.05127031596833942</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1319210265221863</v>
+        <v>0.1319210265221843</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1073911787478613</v>
+        <v>0.1073911787478577</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06477916963252084</v>
+        <v>0.06477916963251865</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07034034035780309</v>
+        <v>0.070340340357801</v>
       </c>
       <c r="V4" t="n">
-        <v>0.09056342132168779</v>
+        <v>0.09056342132168906</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06935338444520556</v>
+        <v>0.06935338444520379</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1189270405277598</v>
+        <v>0.1189270405277584</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06007704781200279</v>
+        <v>0.06007704781200115</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05545519343953272</v>
+        <v>0.05545519343952957</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.09829692293809904</v>
+        <v>0.098296922938097</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.06356180766161799</v>
+        <v>0.06356180766161768</v>
       </c>
     </row>
     <row r="5">
@@ -3586,85 +3586,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03665664442699873</v>
+        <v>0.03665664442699614</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04063850256966468</v>
+        <v>0.04063850256966436</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03866777876545978</v>
+        <v>0.038667778765458</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03722295452574907</v>
+        <v>0.03722295452574871</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03884167046416154</v>
+        <v>0.03884167046416138</v>
       </c>
       <c r="G5" t="n">
-        <v>0.039084800571841</v>
+        <v>0.03908480057183717</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03866777876545978</v>
+        <v>0.038667778765458</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03866777876545978</v>
+        <v>0.038667778765458</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03812899846033625</v>
+        <v>0.03812899846033555</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03866777876545978</v>
+        <v>0.038667778765458</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03866777876545978</v>
+        <v>0.038667778765458</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03834635033379387</v>
+        <v>0.03834635033379431</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03710881319763495</v>
+        <v>0.03710881319763221</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03753723047179271</v>
+        <v>0.03753723047179006</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03743221504589971</v>
+        <v>0.03743221504589791</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03626141062767879</v>
+        <v>0.03626141062767497</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03866777876545978</v>
+        <v>0.038667778765458</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03866777876545978</v>
+        <v>0.038667778765458</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03866777876545978</v>
+        <v>0.038667778765458</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03768716194610577</v>
+        <v>0.03768716194610223</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03645062982249376</v>
+        <v>0.03645062982249554</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03866817401068941</v>
+        <v>0.03866817401068618</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03644573508579853</v>
+        <v>0.03644573508579693</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04066909918998733</v>
+        <v>0.04066909918998578</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03661928657417504</v>
+        <v>0.0366192865741725</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03866777876545978</v>
+        <v>0.038667778765458</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04024107406600973</v>
+        <v>0.04024107406600951</v>
       </c>
     </row>
     <row r="6">
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02521948255600558</v>
+        <v>0.02521948255600261</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2752127923384304</v>
+        <v>0.2752127923384303</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1160615780607436</v>
+        <v>0.1160615780607411</v>
       </c>
       <c r="E6" t="n">
-        <v>0.202758101926077</v>
+        <v>0.2027581019260772</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2893968607861193</v>
+        <v>0.2893968607861191</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03842719764871727</v>
+        <v>0.03842719764871332</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05115660774167169</v>
+        <v>0.05115660774166886</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07058055703007744</v>
+        <v>0.07058055703007469</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0639120620984427</v>
+        <v>0.06391206209844175</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06905267875316909</v>
+        <v>0.06905267875316679</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09596064231200629</v>
+        <v>0.0959606423120038</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07610973695029316</v>
+        <v>0.07610973695029308</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02347244910220464</v>
+        <v>0.02347244910220193</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04491680134332056</v>
+        <v>0.0449168013433171</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05091245741057326</v>
+        <v>0.05091245741057045</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02852050739951972</v>
+        <v>0.02852050739951714</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1091712179533646</v>
+        <v>0.1091712179533617</v>
       </c>
       <c r="S6" t="n">
-        <v>0.08464137017903928</v>
+        <v>0.0846413701790352</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04202936106369923</v>
+        <v>0.04202936106369603</v>
       </c>
       <c r="U6" t="n">
-        <v>0.04531204294026502</v>
+        <v>0.04531204294026126</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06612636507500108</v>
+        <v>0.06612636507500098</v>
       </c>
       <c r="W6" t="n">
-        <v>0.04432508702766759</v>
+        <v>0.04432508702766397</v>
       </c>
       <c r="X6" t="n">
-        <v>0.09389874311021953</v>
+        <v>0.09389874311021824</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03732723924318043</v>
+        <v>0.03732723924317875</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03270538487071033</v>
+        <v>0.03270538487070703</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.07554711436927763</v>
+        <v>0.0755471143692749</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0408119990927952</v>
+        <v>0.04081199909279523</v>
       </c>
     </row>
     <row r="7">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01390683585817496</v>
+        <v>0.01390683585817363</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01788869400084194</v>
+        <v>0.01788869400084193</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01591797019663918</v>
+        <v>0.01591797019663543</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01447314595692621</v>
+        <v>0.0144731459569262</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01609186189533894</v>
+        <v>0.01609186189533892</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0140565031542993</v>
+        <v>0.01405650315429733</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01591797019663918</v>
+        <v>0.01591797019663543</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01591797019663918</v>
+        <v>0.01591797019663543</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01325055172857817</v>
+        <v>0.01325055172857795</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01591797019663918</v>
+        <v>0.01591797019663543</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01591797019663918</v>
+        <v>0.01591797019663543</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01559654176497105</v>
+        <v>0.01559654176497087</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01435900462881091</v>
+        <v>0.01435900462880975</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01250893305425311</v>
+        <v>0.01250893305425033</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01240391762836098</v>
+        <v>0.01240391762835813</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01351160205885457</v>
+        <v>0.01351160205885245</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01591797019663918</v>
+        <v>0.01591797019663543</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01591797019663918</v>
+        <v>0.01591797019663543</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01591797019663918</v>
+        <v>0.01591797019663543</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01265886452856769</v>
+        <v>0.01265886452856261</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01201357357580732</v>
+        <v>0.01201357357580746</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0136398765931484</v>
+        <v>0.01363987659314642</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01141743766825989</v>
+        <v>0.01141743766825719</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01791929062116646</v>
+        <v>0.01791929062116311</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01386947800535315</v>
+        <v>0.01386947800534993</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01591797019663918</v>
+        <v>0.01591797019663543</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01749126549718716</v>
+        <v>0.01749126549718715</v>
       </c>
     </row>
   </sheetData>
@@ -4006,85 +4006,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02301491464065238</v>
+        <v>0.0230149146406523</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9715022961951381</v>
+        <v>0.9715022961951374</v>
       </c>
       <c r="D2" t="n">
         <v>0.3498636644200318</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8732390023803696</v>
+        <v>0.8732390023803706</v>
       </c>
       <c r="F2" t="n">
         <v>1.109059489192187</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07004192375800093</v>
+        <v>0.07004192375800003</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1866291742697846</v>
+        <v>0.186629174269784</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5279456592785785</v>
+        <v>0.527945659278578</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2229440839790674</v>
+        <v>0.2229440839790659</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3026744511627611</v>
+        <v>0.30267445116276</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3621669334496654</v>
+        <v>0.3621669334496638</v>
       </c>
       <c r="M2" t="n">
-        <v>0.424264452926824</v>
+        <v>0.4242644529268235</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05828528904977275</v>
+        <v>0.05828528904977313</v>
       </c>
       <c r="O2" t="n">
-        <v>0.12749078273308</v>
+        <v>0.1274907827330792</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2188983264764356</v>
+        <v>0.2188983264764366</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04354830918682729</v>
+        <v>0.04354830918682644</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3539222395908098</v>
+        <v>0.3539222395908088</v>
       </c>
       <c r="S2" t="n">
         <v>0.4664937851484947</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0976305968949502</v>
+        <v>0.0976305968949488</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1861188724208906</v>
+        <v>0.1861188724208909</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2166615283828236</v>
+        <v>0.2166615283828238</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1815132722560923</v>
+        <v>0.1815132722560921</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2550458784821845</v>
+        <v>0.2550458784821846</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.108655496578721</v>
+        <v>0.1086554965787198</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.089070246404471</v>
+        <v>0.08907024640447118</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.3752949642920168</v>
+        <v>0.3752949642920151</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2660104915026554</v>
+        <v>0.2660104915026556</v>
       </c>
     </row>
     <row r="3">
@@ -4094,85 +4094,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01822641523545224</v>
+        <v>0.018226415235454</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0263038333116127</v>
+        <v>0.02630383331161272</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0239923941074833</v>
+        <v>0.0239923941074809</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02091002450172588</v>
+        <v>0.02091002450172585</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02189920554768023</v>
+        <v>0.0218992055476802</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02518800738839441</v>
+        <v>0.02518800738839156</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0239923941074833</v>
+        <v>0.0239923941074809</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0239923941074833</v>
+        <v>0.0239923941074809</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02347579075149929</v>
+        <v>0.0234757907514988</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0239923941074833</v>
+        <v>0.0239923941074809</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0239923941074833</v>
+        <v>0.0239923941074809</v>
       </c>
       <c r="M3" t="n">
         <v>0.02406295124008957</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01952279585421002</v>
+        <v>0.01952279585421052</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02075108026266179</v>
+        <v>0.02075108026266062</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02044999807468479</v>
+        <v>0.02044999807468376</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01709326878530332</v>
+        <v>0.01709326878529983</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0239923941074833</v>
+        <v>0.0239923941074809</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0239923941074833</v>
+        <v>0.0239923941074809</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0239923941074833</v>
+        <v>0.0239923941074809</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02117964394977358</v>
+        <v>0.02117964394977359</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02104466636004377</v>
+        <v>0.02104466636004351</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02399352728673221</v>
+        <v>0.02399352728672865</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01762173220559295</v>
+        <v>0.01762173220559066</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02972802241961892</v>
+        <v>0.02972802241961486</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01811930921773831</v>
+        <v>0.01811930921773598</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0239923941074833</v>
+        <v>0.0239923941074809</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02982523040785662</v>
+        <v>0.02982523040785661</v>
       </c>
     </row>
     <row r="4">
@@ -4182,85 +4182,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04166092084242563</v>
+        <v>0.04166092084242488</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3888423804743975</v>
+        <v>0.388842380474397</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1607934520852175</v>
+        <v>0.1607934520852126</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3515498917441624</v>
+        <v>0.3515498917441615</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4392746541785437</v>
+        <v>0.4392746541785429</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05880171344667746</v>
+        <v>0.05880171344667641</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1012963972216072</v>
+        <v>0.1012963972216068</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2257022480667951</v>
+        <v>0.2257022480667943</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1143523688710317</v>
+        <v>0.114352368871033</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1435935379766564</v>
+        <v>0.1435935379766566</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1652778491742358</v>
+        <v>0.165277849174236</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1879565057240698</v>
+        <v>0.1879565057240694</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05451655814890242</v>
+        <v>0.05451655814890274</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07974114794453219</v>
+        <v>0.07974114794453185</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1130581242774204</v>
+        <v>0.1130581242774154</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.049145102039213</v>
+        <v>0.04914510203921298</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1622727550767665</v>
+        <v>0.1622727550767662</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2033037615507173</v>
+        <v>0.2033037615507156</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06885746084254289</v>
+        <v>0.06885746084253841</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1011103981899528</v>
+        <v>0.1011103981899518</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1123568539165753</v>
+        <v>0.1123568539165746</v>
       </c>
       <c r="W4" t="n">
-        <v>0.09943171101157933</v>
+        <v>0.09943171101157049</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1262334825175246</v>
+        <v>0.1262334825175245</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07287590731636354</v>
+        <v>0.07287590731636463</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06573731360947103</v>
+        <v>0.06573731360946987</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1700628622591538</v>
+        <v>0.1700628622591521</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1301090740300705</v>
+        <v>0.1301090740300709</v>
       </c>
     </row>
     <row r="5">
@@ -4270,85 +4270,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0399155690386308</v>
+        <v>0.03991556903862935</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04432863983407302</v>
+        <v>0.04432863983407252</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04201720062994384</v>
+        <v>0.04201720062994062</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0408859878595642</v>
+        <v>0.04088598785956368</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04301749687070317</v>
+        <v>0.04301749687070296</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04245298763123566</v>
+        <v>0.04245298763123263</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04201720062994384</v>
+        <v>0.04201720062994062</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04201720062994384</v>
+        <v>0.04201720062994062</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04164851826453933</v>
+        <v>0.04164851826454001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04201720062994384</v>
+        <v>0.04201720062994062</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04201720062994384</v>
+        <v>0.04201720062994062</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04208775776255035</v>
+        <v>0.04208775776255009</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04038808455129912</v>
+        <v>0.04038808455129595</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04083577979493093</v>
+        <v>0.04083577979493255</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04072603887289908</v>
+        <v>0.04072603887290039</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03950255046362431</v>
+        <v>0.03950255046362546</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04201720062994384</v>
+        <v>0.04201720062994062</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04201720062994384</v>
+        <v>0.04201720062994062</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04201720062994384</v>
+        <v>0.04201720062994062</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04099198622643394</v>
+        <v>0.04099198622643604</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04105680475843905</v>
+        <v>0.04105680475843896</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04201761366046913</v>
+        <v>0.04201761366046966</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03969516917479226</v>
+        <v>0.03969516917479028</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04410776979856788</v>
+        <v>0.04410776979856559</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03987653015287169</v>
+        <v>0.03987653015287335</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04201720062994384</v>
+        <v>0.04201720062994062</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0440223197883761</v>
+        <v>0.04402231978837656</v>
       </c>
     </row>
     <row r="6">
@@ -4358,85 +4358,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01648412352369428</v>
+        <v>0.01648412352369381</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3636655831556672</v>
+        <v>0.3636655831556675</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1356166547664853</v>
+        <v>0.1356166547664819</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3263730944254304</v>
+        <v>0.3263730944254302</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4140978568598134</v>
+        <v>0.4140978568598133</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03134546179133169</v>
+        <v>0.03134546179133162</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07611959990287728</v>
+        <v>0.07611959990287623</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2005254507480649</v>
+        <v>0.2005254507480635</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08682526233686513</v>
+        <v>0.08682526233686631</v>
       </c>
       <c r="K6" t="n">
-        <v>0.118416740657926</v>
+        <v>0.1184167406579255</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1401010518555067</v>
+        <v>0.140101051855505</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1627797084053382</v>
+        <v>0.1627797084053381</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02933976083017215</v>
+        <v>0.02933976083017178</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0522848962891873</v>
+        <v>0.05228489628918696</v>
       </c>
       <c r="P6" t="n">
-        <v>0.08560187262207535</v>
+        <v>0.08560187262207034</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0239683047204818</v>
+        <v>0.02396830472048222</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1370959577580354</v>
+        <v>0.1370959577580356</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1781269642319862</v>
+        <v>0.1781269642319849</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04368066352380839</v>
+        <v>0.04368066352380744</v>
       </c>
       <c r="U6" t="n">
-        <v>0.07365414653460695</v>
+        <v>0.07365414653460708</v>
       </c>
       <c r="V6" t="n">
-        <v>0.08401871279040701</v>
+        <v>0.08401871279040742</v>
       </c>
       <c r="W6" t="n">
-        <v>0.07197545935623038</v>
+        <v>0.07197545935622562</v>
       </c>
       <c r="X6" t="n">
-        <v>0.09877723086218045</v>
+        <v>0.09877723086217924</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.04769910999763396</v>
+        <v>0.04769910999763338</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.04056051629073856</v>
+        <v>0.04056051629073877</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1448860649404206</v>
+        <v>0.1448860649404203</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1049322767113398</v>
+        <v>0.1049322767113397</v>
       </c>
     </row>
     <row r="7">
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01473877171990145</v>
+        <v>0.01473877171989836</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0191518425153415</v>
+        <v>0.01915184251534151</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01684040331121227</v>
+        <v>0.0168404033112095</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01570919054083273</v>
+        <v>0.0157091905408327</v>
       </c>
       <c r="F7" t="n">
-        <v>0.017840699551972</v>
+        <v>0.01784069955197204</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01499673597588865</v>
+        <v>0.01499673597588768</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01684040331121227</v>
+        <v>0.0168404033112095</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01684040331121227</v>
+        <v>0.0168404033112095</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01412141173037488</v>
+        <v>0.01412141173037327</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01684040331121227</v>
+        <v>0.0168404033112095</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01684040331121227</v>
+        <v>0.0168404033112095</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01691096044381918</v>
+        <v>0.01691096044381916</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01521128723256464</v>
+        <v>0.01521128723256494</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01337952813958587</v>
+        <v>0.0133795281395875</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01326978721755286</v>
+        <v>0.01326978721755523</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01432575314489273</v>
+        <v>0.01432575314489429</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01684040331121227</v>
+        <v>0.0168404033112095</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01684040331121227</v>
+        <v>0.0168404033112095</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01684040331121227</v>
+        <v>0.0168404033112095</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0135357345710889</v>
+        <v>0.013535734571091</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01271866363227095</v>
+        <v>0.01271866363227089</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01456136200512517</v>
+        <v>0.01456136200512472</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01223891751944723</v>
+        <v>0.01223891751944525</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01893097247983336</v>
+        <v>0.01893097247983461</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01469973283414133</v>
+        <v>0.01469973283414232</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01684040331121227</v>
+        <v>0.0168404033112095</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01884552246964553</v>
+        <v>0.01884552246964551</v>
       </c>
     </row>
   </sheetData>
@@ -4690,82 +4690,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02247199928442708</v>
+        <v>0.0224719992844264</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7741557423477106</v>
+        <v>0.7741557423477108</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1976347602423491</v>
+        <v>0.1976347602423484</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5310392055342278</v>
+        <v>0.5310392055342276</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8793882198076375</v>
+        <v>0.8793882198076384</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05537742632632081</v>
+        <v>0.05537742632631776</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1435968586992804</v>
+        <v>0.1435968586992797</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2399194007900103</v>
+        <v>0.2399194007900098</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1700799180017604</v>
+        <v>0.1700799180017599</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1708388035765349</v>
+        <v>0.1708388035765341</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1931847742276209</v>
+        <v>0.1931847742276201</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2647175883777874</v>
+        <v>0.2647175883777871</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05582846746226561</v>
+        <v>0.05582846746226512</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1314745641139454</v>
+        <v>0.1314745641139446</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2043295860751005</v>
+        <v>0.2043295860750996</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03055598433962112</v>
+        <v>0.03055598433962064</v>
       </c>
       <c r="R2" t="n">
-        <v>0.228201012764376</v>
+        <v>0.2282010127643749</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3113493582765985</v>
+        <v>0.3113493582765975</v>
       </c>
       <c r="T2" t="n">
-        <v>0.07726801860514962</v>
+        <v>0.07726801860514948</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1655470785757231</v>
+        <v>0.1655470785757224</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1798290658832064</v>
+        <v>0.1798290658832059</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1273779867063174</v>
+        <v>0.1273779867063166</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2227763075492512</v>
+        <v>0.2227763075492507</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.08397824778597551</v>
+        <v>0.08397824778597496</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.05320353015024538</v>
+        <v>0.05320353015024452</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1600599879024933</v>
+        <v>0.1600599879024925</v>
       </c>
       <c r="AB2" t="n">
         <v>0.1829313098463392</v>
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01683241587423158</v>
+        <v>0.01683241587423184</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02441240717857192</v>
+        <v>0.02441240717857099</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02229995715619192</v>
+        <v>0.02229995715619029</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01905012261911666</v>
+        <v>0.01905012261911658</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01997921560125388</v>
+        <v>0.01997921560125384</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02343368745866347</v>
+        <v>0.02343368745866376</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02229995715619192</v>
+        <v>0.02229995715619029</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02229995715619192</v>
+        <v>0.02229995715619029</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02187704028167749</v>
+        <v>0.0218770402816768</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02229995715619192</v>
+        <v>0.02229995715619029</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02229995715619192</v>
+        <v>0.02229995715619029</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02222975417332725</v>
+        <v>0.02222975417332717</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01806169796275212</v>
+        <v>0.01806169796275188</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01922640838889656</v>
+        <v>0.01922640838889539</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01894090972014312</v>
+        <v>0.0189409097201432</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01575791922201942</v>
+        <v>0.01575791922201949</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02229995715619192</v>
+        <v>0.02229995715619029</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02229995715619192</v>
+        <v>0.02229995715619029</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02229995715619192</v>
+        <v>0.02229995715619029</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0196332086854542</v>
+        <v>0.01963320868545391</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01969373424025078</v>
+        <v>0.01969373424024989</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02230103168393808</v>
+        <v>0.0223010316839375</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01625903024419853</v>
+        <v>0.01625903024419779</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02773943446824411</v>
+        <v>0.02773943446824329</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01673085348796254</v>
+        <v>0.01673085348796207</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02229995715619192</v>
+        <v>0.02229995715619029</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02784704854057594</v>
+        <v>0.02784704854057583</v>
       </c>
     </row>
     <row r="4">
@@ -4866,85 +4866,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03695413222416288</v>
+        <v>0.03695413222416215</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3122765166494397</v>
+        <v>0.3122765166494383</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1007989017283395</v>
+        <v>0.1007989017283388</v>
       </c>
       <c r="E4" t="n">
         <v>0.2221057671590707</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3507485447883024</v>
+        <v>0.3507485447883026</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04894777398589963</v>
+        <v>0.04894777398589917</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08110272116096774</v>
+        <v>0.08110272116096695</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1162111566766444</v>
+        <v>0.1162111566766438</v>
       </c>
       <c r="J4" t="n">
-        <v>0.09075045210095588</v>
+        <v>0.09075045210095599</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09103209017765986</v>
+        <v>0.09103209017765926</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09917693408034531</v>
+        <v>0.09917693408034464</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1252051900373931</v>
+        <v>0.1252051900373929</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04911217318356053</v>
+        <v>0.04911217318355945</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07668428713178305</v>
+        <v>0.07668428713178234</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1032390871297636</v>
+        <v>0.103239087129763</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0399006498498359</v>
+        <v>0.03990064984983662</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1119399418455597</v>
+        <v>0.1119399418455589</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1422465374075969</v>
+        <v>0.1422465374075963</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05692663781922103</v>
+        <v>0.05692663781922081</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08910331855343591</v>
+        <v>0.08910331855343513</v>
       </c>
       <c r="V4" t="n">
-        <v>0.09536059192388761</v>
+        <v>0.09536059192388682</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07519113277114321</v>
+        <v>0.07519113277114242</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1099627004947521</v>
+        <v>0.1099627004947514</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05937243756014286</v>
+        <v>0.0593724375601422</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04815541435689889</v>
+        <v>0.04815541435689817</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.08710333843571547</v>
+        <v>0.0871033384357148</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.09533530763413754</v>
+        <v>0.09533530763413753</v>
       </c>
     </row>
     <row r="5">
@@ -4954,85 +4954,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03489857029447837</v>
+        <v>0.03489857029447624</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03900387491102232</v>
+        <v>0.03900387491102019</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03689142488864192</v>
+        <v>0.03689142488864081</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03549175851586095</v>
+        <v>0.035491758515861</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03750405444511132</v>
+        <v>0.03750405444511119</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03730465627095934</v>
+        <v>0.037304656270959</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03689142488864192</v>
+        <v>0.03689142488864081</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03689142488864192</v>
+        <v>0.03689142488864081</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03673224345803963</v>
+        <v>0.03673224345803959</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03689142488864192</v>
+        <v>0.03689142488864081</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03689142488864192</v>
+        <v>0.03689142488864081</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03682122190577762</v>
+        <v>0.03682122190577757</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03534662918078475</v>
+        <v>0.03534662918078484</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0357711524543939</v>
+        <v>0.03577115245439437</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03566709154212825</v>
+        <v>0.03566709154212857</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03450692888212406</v>
+        <v>0.03450692888212335</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03689142488864192</v>
+        <v>0.03689142488864081</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03689142488864192</v>
+        <v>0.03689142488864081</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03689142488864192</v>
+        <v>0.03689142488864081</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03591942638559927</v>
+        <v>0.03591942638559945</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03699314394403124</v>
+        <v>0.03699314394403062</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03689181654138778</v>
+        <v>0.03689181654138737</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03468957796536588</v>
+        <v>0.03468957796536445</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03887405049531721</v>
+        <v>0.03887405049531645</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03486155199728927</v>
+        <v>0.03486155199728908</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03689142488864192</v>
+        <v>0.03689142488864081</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03880891547952646</v>
+        <v>0.03880891547952645</v>
       </c>
     </row>
     <row r="6">
@@ -5042,85 +5042,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01569446742549124</v>
+        <v>0.01569446742549068</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2910168518507674</v>
+        <v>0.2910168518507667</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07953923692966808</v>
+        <v>0.07953923692966748</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2008461023603986</v>
+        <v>0.2008461023603985</v>
       </c>
       <c r="F6" t="n">
-        <v>0.329488879989632</v>
+        <v>0.3294888799896323</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02541301722012387</v>
+        <v>0.02541301722012242</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05984305636229616</v>
+        <v>0.0598430563622955</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09495149187797243</v>
+        <v>0.09495149187797197</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06702877136290941</v>
+        <v>0.06702877136290891</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06977242537898803</v>
+        <v>0.06977242537898738</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07791726928167329</v>
+        <v>0.07791726928167275</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1039455252387215</v>
+        <v>0.1039455252387214</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02785250838488801</v>
+        <v>0.02785250838488787</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05314953036600621</v>
+        <v>0.05314953036600569</v>
       </c>
       <c r="P6" t="n">
-        <v>0.07970433036398661</v>
+        <v>0.07970433036398603</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01864098505116426</v>
+        <v>0.01864098505116495</v>
       </c>
       <c r="R6" t="n">
-        <v>0.09068027704688773</v>
+        <v>0.09068027704688712</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1209868726089251</v>
+        <v>0.1209868726089246</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03566697302054939</v>
+        <v>0.03566697302054929</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06556856178765927</v>
+        <v>0.06556856178765877</v>
       </c>
       <c r="V6" t="n">
-        <v>0.07017079178260913</v>
+        <v>0.07017079178260936</v>
       </c>
       <c r="W6" t="n">
-        <v>0.05165637600536637</v>
+        <v>0.05165637600536577</v>
       </c>
       <c r="X6" t="n">
-        <v>0.08642794372897512</v>
+        <v>0.08642794372897436</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03811277276147105</v>
+        <v>0.03811277276147043</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02689574955822711</v>
+        <v>0.02689574955822645</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.06584367363704374</v>
+        <v>0.0658436736370431</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.07407564283546625</v>
+        <v>0.07407564283546618</v>
       </c>
     </row>
     <row r="7">
@@ -5130,85 +5130,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01363890549580678</v>
+        <v>0.01363890549580468</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01774421011235056</v>
+        <v>0.01774421011234913</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01563176008996962</v>
+        <v>0.01563176008996912</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01423209371718927</v>
+        <v>0.01423209371718922</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01624438964643966</v>
+        <v>0.01624438964643962</v>
       </c>
       <c r="G7" t="n">
-        <v>0.013769899505183</v>
+        <v>0.01376989950518227</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01563176008996962</v>
+        <v>0.01563176008996912</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01563176008996962</v>
+        <v>0.01563176008996912</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0130105627199924</v>
+        <v>0.01301056271999151</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01563176008996962</v>
+        <v>0.01563176008996912</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01563176008996962</v>
+        <v>0.01563176008996912</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01556155710710596</v>
+        <v>0.0155615571071059</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01408696438211384</v>
+        <v>0.01408696438211319</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01223639568861791</v>
+        <v>0.0122363956886178</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01213233477635174</v>
+        <v>0.01213233477635186</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01324726408345164</v>
+        <v>0.01324726408345174</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01563176008996962</v>
+        <v>0.01563176008996912</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01563176008996962</v>
+        <v>0.01563176008996912</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01563176008996962</v>
+        <v>0.01563176008996912</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01238466961982257</v>
+        <v>0.01238466961982278</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01180334380275354</v>
+        <v>0.01180334380275316</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01335705977561111</v>
+        <v>0.01335705977561061</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0111548211995884</v>
+        <v>0.01115482119958776</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01761438569664544</v>
+        <v>0.0176143856966448</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01360188719861812</v>
+        <v>0.01360188719861743</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01563176008996962</v>
+        <v>0.01563176008996912</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01754925068085477</v>
+        <v>0.01754925068085473</v>
       </c>
     </row>
   </sheetData>
@@ -5374,85 +5374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02464299580508618</v>
+        <v>0.02464299580508605</v>
       </c>
       <c r="C2" t="n">
-        <v>0.691173646369715</v>
+        <v>0.6911736463697156</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1624719777853511</v>
+        <v>0.1624719777853506</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2387461023294786</v>
+        <v>0.2387461023294788</v>
       </c>
       <c r="F2" t="n">
         <v>0.7463295297161032</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03704732280927243</v>
+        <v>0.03704732280927213</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1154254902723489</v>
+        <v>0.1154254902723497</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1207080721293933</v>
+        <v>0.1207080721293932</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1314540251435607</v>
+        <v>0.1314540251435616</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1129077044850135</v>
+        <v>0.1129077044850133</v>
       </c>
       <c r="L2" t="n">
         <v>0.1734459987064269</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1938778776587471</v>
+        <v>0.1938778776587474</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03962960593899571</v>
+        <v>0.03962960593899563</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1132309079864376</v>
+        <v>0.1132309079864375</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1874681265884669</v>
+        <v>0.187468126588467</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02342745203505268</v>
+        <v>0.02342745203505253</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1549473238156107</v>
+        <v>0.1549473238156105</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2399833164454994</v>
+        <v>0.2399833164454986</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06676468704088614</v>
+        <v>0.06676468704088603</v>
       </c>
       <c r="U2" t="n">
-        <v>0.13424367440906</v>
+        <v>0.1342436744090597</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1302928037353745</v>
+        <v>0.1302928037353746</v>
       </c>
       <c r="W2" t="n">
-        <v>0.07561369269083634</v>
+        <v>0.07561369269083619</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1808792749634453</v>
+        <v>0.1808792749634458</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.06449600974036658</v>
+        <v>0.06449600974036648</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03083747318083162</v>
+        <v>0.03083747318083109</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.07410561759004941</v>
+        <v>0.07410561759004949</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1088222982613336</v>
+        <v>0.1088222982613335</v>
       </c>
     </row>
     <row r="3">
@@ -5462,82 +5462,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01579118660182057</v>
+        <v>0.01579118660182102</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02312016284543463</v>
+        <v>0.02312016284543458</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02103507178777471</v>
+        <v>0.02103507178777451</v>
       </c>
       <c r="E3" t="n">
         <v>0.01755196795522842</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01863884692359798</v>
+        <v>0.01863884692359797</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02212242554176223</v>
+        <v>0.02212242554176216</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02103507178777471</v>
+        <v>0.02103507178777451</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02103507178777471</v>
+        <v>0.02103507178777451</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02065617461758096</v>
+        <v>0.02065617461758137</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02103507178777471</v>
+        <v>0.02103507178777451</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02103507178777471</v>
+        <v>0.02103507178777451</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02095559112242145</v>
+        <v>0.0209555911224217</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01697018348561084</v>
+        <v>0.01697018348561029</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01808725008552296</v>
+        <v>0.01808725008552123</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01781343006980971</v>
+        <v>0.01781343006980942</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01476064347715151</v>
+        <v>0.01476064347715086</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02103507178777471</v>
+        <v>0.02103507178777451</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02103507178777471</v>
+        <v>0.02103507178777451</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02103507178777471</v>
+        <v>0.02103507178777451</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01847673809972424</v>
+        <v>0.01847673809972462</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01860439652598174</v>
+        <v>0.01860439652598168</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02103610236077524</v>
+        <v>0.02103610236077356</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01524125597377081</v>
+        <v>0.015241255973771</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0262508920020671</v>
+        <v>0.02625089200206621</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01569377874235189</v>
+        <v>0.0156937787423521</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02103507178777471</v>
+        <v>0.02103507178777451</v>
       </c>
       <c r="AB3" t="n">
         <v>0.02628651321414355</v>
@@ -5550,85 +5550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03467684415482821</v>
+        <v>0.03467684415482811</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2789445393390957</v>
+        <v>0.2789445393390956</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08491388961701557</v>
+        <v>0.08491388961701535</v>
       </c>
       <c r="E4" t="n">
-        <v>0.112275843868062</v>
+        <v>0.1122758438680621</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2990136604306193</v>
+        <v>0.2990136604306197</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03919807568889259</v>
+        <v>0.03919807568889253</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06776599736627473</v>
+        <v>0.06776599736627459</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06969143642195891</v>
+        <v>0.06969143642195892</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07344274441026119</v>
+        <v>0.07344274441026116</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06684829401212378</v>
+        <v>0.06684829401212318</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08891379137928737</v>
+        <v>0.0889137913792875</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09631046043803083</v>
+        <v>0.09631046043803113</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04013928756697711</v>
+        <v>0.04013928756697709</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06696609789314607</v>
+        <v>0.06696609789314599</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09402469233615268</v>
+        <v>0.09402469233615261</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03423379272428663</v>
+        <v>0.03423379272428658</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08217124160399304</v>
+        <v>0.08217124160399303</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1131658623745474</v>
+        <v>0.1131658623745469</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05002970599240668</v>
+        <v>0.05002970599240667</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07462500450983089</v>
+        <v>0.07462500450983037</v>
       </c>
       <c r="V4" t="n">
-        <v>0.07305284684039867</v>
+        <v>0.0730528468403993</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05325506464154296</v>
+        <v>0.05325506464154279</v>
       </c>
       <c r="X4" t="n">
-        <v>0.09162313328903551</v>
+        <v>0.0916231332890346</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.04920279975652115</v>
+        <v>0.04920279975652084</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03693465841906166</v>
+        <v>0.03693465841906161</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05270538897601814</v>
+        <v>0.05270538897601774</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.06521543633119189</v>
+        <v>0.06521543633119177</v>
       </c>
     </row>
     <row r="5">
@@ -5638,82 +5638,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03145046364342963</v>
+        <v>0.03145046364342981</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03544688927456095</v>
+        <v>0.03544688927456105</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03336179821690066</v>
+        <v>0.03336179821690108</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03165317928131013</v>
+        <v>0.0316531792813102</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03377895152816438</v>
+        <v>0.03377895152816443</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03375812589187663</v>
+        <v>0.03375812589187745</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03336179821690066</v>
+        <v>0.03336179821690108</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03336179821690066</v>
+        <v>0.03336179821690108</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03305822894758978</v>
+        <v>0.03305822894758968</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03336179821690066</v>
+        <v>0.03336179821690108</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03336179821690066</v>
+        <v>0.03336179821690108</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03328231755154706</v>
+        <v>0.03328231755154737</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03188019416308994</v>
+        <v>0.03188019416308993</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03228735182149969</v>
+        <v>0.03228735182149978</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03218754764113095</v>
+        <v>0.03218754764112986</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03107484277573601</v>
+        <v>0.03107484277573587</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03336179821690066</v>
+        <v>0.03336179821690108</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03336179821690066</v>
+        <v>0.03336179821690108</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03336179821690066</v>
+        <v>0.03336179821690108</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03242931562907796</v>
+        <v>0.03242931562907739</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03234373392406792</v>
+        <v>0.03234373392406872</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0333621738486574</v>
+        <v>0.03336217384865748</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03125002038711748</v>
+        <v>0.03125002038711655</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03526290343775772</v>
+        <v>0.03526290343775697</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03141495962247436</v>
+        <v>0.03141495962247412</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03336179821690066</v>
+        <v>0.03336179821690108</v>
       </c>
       <c r="AB5" t="n">
         <v>0.03513211186561122</v>
@@ -5726,85 +5726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01604365861931112</v>
+        <v>0.01604365861930959</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2603113538035776</v>
+        <v>0.2603113538035775</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06628070408149835</v>
+        <v>0.0662807040814966</v>
       </c>
       <c r="E6" t="n">
         <v>0.09364265833254318</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2803804748950999</v>
+        <v>0.2803804748951001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01829389580177976</v>
+        <v>0.01829389580177986</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0491328118307575</v>
+        <v>0.04913281183075602</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05105825088644171</v>
+        <v>0.05105825088644023</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05253976395287849</v>
+        <v>0.05253976395287824</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04821510847660673</v>
+        <v>0.04821510847660467</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07028060584377055</v>
+        <v>0.07028060584376901</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07767727490251229</v>
+        <v>0.07767727490251254</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02150610203146006</v>
+        <v>0.02150610203145851</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04606191800603346</v>
+        <v>0.04606191800603325</v>
       </c>
       <c r="P6" t="n">
-        <v>0.07312051244904022</v>
+        <v>0.07312051244904008</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01560060718876955</v>
+        <v>0.015600607188768</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06353805606847564</v>
+        <v>0.06353805606847411</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09453267683903033</v>
+        <v>0.09453267683902837</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03139652045688956</v>
+        <v>0.031396520456888</v>
       </c>
       <c r="U6" t="n">
-        <v>0.05372082462271822</v>
+        <v>0.05372082462271754</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0517500777070189</v>
+        <v>0.05175007770701887</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0323508847544304</v>
+        <v>0.03235088475443019</v>
       </c>
       <c r="X6" t="n">
-        <v>0.07071895340192275</v>
+        <v>0.07071895340192189</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03056961422100406</v>
+        <v>0.03056961422100238</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01830147288354397</v>
+        <v>0.01830147288354288</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03407220344050101</v>
+        <v>0.03407220344049904</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.04658225079567317</v>
+        <v>0.04658225079567304</v>
       </c>
     </row>
     <row r="7">
@@ -5814,85 +5814,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01281727810791125</v>
+        <v>0.01281727810791124</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01681370373904246</v>
+        <v>0.01681370373904241</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01472861268138205</v>
+        <v>0.01472861268138238</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01301999374579168</v>
+        <v>0.01301999374579165</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01514576599264593</v>
+        <v>0.0151457659926459</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01285394600476402</v>
+        <v>0.01285394600476476</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01472861268138205</v>
+        <v>0.01472861268138238</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01472861268138205</v>
+        <v>0.01472861268138238</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01215524849020702</v>
+        <v>0.0121552484902068</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01472861268138205</v>
+        <v>0.01472861268138238</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01472861268138205</v>
+        <v>0.01472861268138238</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01464913201602854</v>
+        <v>0.01464913201602877</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01324700862757255</v>
+        <v>0.01324700862757143</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01138317193438707</v>
+        <v>0.01138317193438715</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01128336775401838</v>
+        <v>0.01128336775401723</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01244165724021758</v>
+        <v>0.01244165724021722</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01472861268138205</v>
+        <v>0.01472861268138238</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01472861268138205</v>
+        <v>0.01472861268138238</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01472861268138205</v>
+        <v>0.01472861268138238</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01152513574196551</v>
+        <v>0.01152513574196479</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01104096479068817</v>
+        <v>0.01104096479068811</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0124579939615448</v>
+        <v>0.01245799396154481</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01034584050000486</v>
+        <v>0.01034584050000379</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01662971790223961</v>
+        <v>0.01662971790223843</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01278177408695544</v>
+        <v>0.01278177408695545</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01472861268138205</v>
+        <v>0.01472861268138238</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01649892633009268</v>
+        <v>0.0164989263300926</v>
       </c>
     </row>
   </sheetData>
@@ -6058,82 +6058,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04322458119865961</v>
+        <v>0.04322458119866902</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9401402960950289</v>
+        <v>0.9401402960950376</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6277302048241378</v>
+        <v>0.6277302048241453</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8334825776169896</v>
+        <v>0.8334825776169924</v>
       </c>
       <c r="F2" t="n">
         <v>1.028174380228136</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1055626334608317</v>
+        <v>0.1055626334608416</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1684862077599033</v>
+        <v>0.1684862077599127</v>
       </c>
       <c r="I2" t="n">
-        <v>0.457651770345418</v>
+        <v>0.4576517703454255</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2032157990088011</v>
+        <v>0.2032157990088052</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2787598112750844</v>
+        <v>0.2787598112750934</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2981060172677812</v>
+        <v>0.2981060172677897</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2073786277180421</v>
+        <v>0.2073786277180422</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05041542779219752</v>
+        <v>0.05041542779220558</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1101832822419044</v>
+        <v>0.1101832822419122</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1645067353799758</v>
+        <v>0.1645067353799807</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04325805760454033</v>
+        <v>0.04325805760454859</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3253084608665527</v>
+        <v>0.32530846086655</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3386760775651836</v>
+        <v>0.3386760775651919</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06904538540833412</v>
+        <v>0.06904538540834304</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2080106011164523</v>
+        <v>0.2080106011164644</v>
       </c>
       <c r="V2" t="n">
-        <v>0.217236059997688</v>
+        <v>0.2172360599976888</v>
       </c>
       <c r="W2" t="n">
-        <v>0.169683426485269</v>
+        <v>0.1696834264852786</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2469101480306509</v>
+        <v>0.2469101480306599</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1095978758992206</v>
+        <v>0.1095978758992282</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.09459556064955911</v>
+        <v>0.09459556064956713</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.3670686028845035</v>
+        <v>0.3670686028845109</v>
       </c>
       <c r="AB2" t="n">
         <v>0.1492713949504145</v>
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01842834842279239</v>
+        <v>0.01842834842280319</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02633223148810998</v>
+        <v>0.02633223148811161</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02414793791580526</v>
+        <v>0.02414793791581281</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02095773186387256</v>
+        <v>0.02095773186387436</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02175602771761442</v>
+        <v>0.02175602771761444</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02533393205678325</v>
+        <v>0.02533393205678659</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02414793791580526</v>
+        <v>0.02414793791581281</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02414793791580526</v>
+        <v>0.02414793791581281</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02357224916105856</v>
+        <v>0.02357224916106131</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02414793791580526</v>
+        <v>0.02414793791581281</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02414793791580526</v>
+        <v>0.02414793791581281</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02356423988678659</v>
+        <v>0.02356423988678666</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01971429919205351</v>
+        <v>0.01971429919205975</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02093270160958084</v>
+        <v>0.02093270160958385</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02063404173635867</v>
+        <v>0.02063404173636839</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01730431854438886</v>
+        <v>0.01730431854439047</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02414793791580526</v>
+        <v>0.02414793791581281</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02414793791580526</v>
+        <v>0.02414793791581281</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02414793791580526</v>
+        <v>0.02414793791581281</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02135661007524985</v>
+        <v>0.02135661007525204</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02115031001984482</v>
+        <v>0.02115031001984601</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02414906197824881</v>
+        <v>0.02414906197825993</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01782853028593963</v>
+        <v>0.0178285302859525</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02983535573889901</v>
+        <v>0.02983535573890423</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01832210411160142</v>
+        <v>0.01832210411160399</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02414793791580526</v>
+        <v>0.02414793791581281</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0294636067423966</v>
+        <v>0.02946360674239665</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05095505547748596</v>
+        <v>0.05095505547750284</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3792584456556139</v>
+        <v>0.3792584456556267</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2640004916774111</v>
+        <v>0.2640004916774304</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3389028611618978</v>
+        <v>0.3389028611619034</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4115062009410268</v>
+        <v>0.4115062009410313</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07367654351668092</v>
+        <v>0.07367654351669364</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09661144746277762</v>
+        <v>0.09661144746279095</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2020088994717279</v>
+        <v>0.2020088994717467</v>
       </c>
       <c r="J4" t="n">
-        <v>0.108781379193468</v>
+        <v>0.1087813791934686</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1368048810460311</v>
+        <v>0.1368048810460458</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1438563459557496</v>
+        <v>0.1438563459557629</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1104163308880984</v>
+        <v>0.1104163308881077</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05357603462164702</v>
+        <v>0.05357603462166124</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07536071573898381</v>
+        <v>0.07536071573899721</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09516097650961854</v>
+        <v>0.09516097650963165</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0509672572343304</v>
+        <v>0.05096725723434507</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1537713172202811</v>
+        <v>0.1537713172202931</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1586436565364527</v>
+        <v>0.1586436565364651</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06036643540872111</v>
+        <v>0.06036643540873569</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1110176247223805</v>
+        <v>0.1110176247223946</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1126495193823953</v>
+        <v>0.1126495193823952</v>
       </c>
       <c r="W4" t="n">
-        <v>0.09704781962972141</v>
+        <v>0.09704781962974054</v>
       </c>
       <c r="X4" t="n">
-        <v>0.125196052791065</v>
+        <v>0.1251960527910789</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0751473420012638</v>
+        <v>0.07514734200128209</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06967917425884215</v>
+        <v>0.06967917425886035</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1689923986134801</v>
+        <v>0.1689923986134982</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.08918912200705066</v>
+        <v>0.08918912200705721</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04191711980274783</v>
+        <v>0.04191711980276836</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04618613658244581</v>
+        <v>0.04618613658245543</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04400184301014107</v>
+        <v>0.04400184301015277</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04274709603333846</v>
+        <v>0.04274709603335011</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04467852941189997</v>
+        <v>0.04467852941190269</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04443412394788103</v>
+        <v>0.04443412394789486</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04400184301014107</v>
+        <v>0.04400184301015277</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04400184301014107</v>
+        <v>0.04400184301015277</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04330341475503113</v>
+        <v>0.04330341475504608</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04400184301014107</v>
+        <v>0.04400184301015277</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04400184301014107</v>
+        <v>0.04400184301015277</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04341814498112324</v>
+        <v>0.04341814498112731</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0423858337577477</v>
+        <v>0.04238583375775902</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04282992713173311</v>
+        <v>0.04282992713173644</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04272106911498492</v>
+        <v>0.04272106911499696</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04150742411109538</v>
+        <v>0.04150742411111164</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04400184301014107</v>
+        <v>0.04400184301015277</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04400184301014107</v>
+        <v>0.04400184301015277</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04400184301014107</v>
+        <v>0.04400184301015277</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04298443678968514</v>
+        <v>0.04298443678970412</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04117856607059874</v>
+        <v>0.04117856607059997</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04400225271770188</v>
+        <v>0.04400225271771451</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04169849313528638</v>
+        <v>0.04169849313530801</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04607484002162682</v>
+        <v>0.04607484002163122</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04187839499890346</v>
+        <v>0.04187839499892262</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04400184301014107</v>
+        <v>0.04400184301015277</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.04552059005930582</v>
+        <v>0.04552059005931417</v>
       </c>
     </row>
     <row r="6">
@@ -6410,85 +6410,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02402311344384149</v>
+        <v>0.02402311344385191</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3523265036219723</v>
+        <v>0.352326503621974</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2370685496437677</v>
+        <v>0.237068549643778</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3119709191282544</v>
+        <v>0.3119709191282556</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3845742589073825</v>
+        <v>0.3845742589073823</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04446707266615893</v>
+        <v>0.04446707266616817</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06967950542913384</v>
+        <v>0.06967950542914252</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1750769574380834</v>
+        <v>0.1750769574380929</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07977169948710944</v>
+        <v>0.07977169948711596</v>
       </c>
       <c r="K6" t="n">
-        <v>0.109872939012388</v>
+        <v>0.1098729390123958</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1169244039221062</v>
+        <v>0.1169244039221141</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08348438885445407</v>
+        <v>0.08348438885445417</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02664409258800254</v>
+        <v>0.02664409258801112</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04615124488846242</v>
+        <v>0.04615124488847259</v>
       </c>
       <c r="P6" t="n">
-        <v>0.06595150565909656</v>
+        <v>0.06595150565910041</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02403531520068548</v>
+        <v>0.02403531520069475</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1268393751866376</v>
+        <v>0.1268393751866466</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1317117145028081</v>
+        <v>0.1317117145028165</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03343449337507717</v>
+        <v>0.03343449337508612</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08180815387185876</v>
+        <v>0.08180815387186509</v>
       </c>
       <c r="V6" t="n">
-        <v>0.08436397557727686</v>
+        <v>0.08436397557727647</v>
       </c>
       <c r="W6" t="n">
-        <v>0.06783834877919996</v>
+        <v>0.06783834877921258</v>
       </c>
       <c r="X6" t="n">
-        <v>0.09598658194054284</v>
+        <v>0.09598658194055365</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.04821539996762</v>
+        <v>0.04821539996762881</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.04274723222519804</v>
+        <v>0.04274723222520715</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.142060456579836</v>
+        <v>0.1420604565798452</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.06225717997340611</v>
+        <v>0.0622571799734062</v>
       </c>
     </row>
     <row r="7">
@@ -6498,85 +6498,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01498517776910387</v>
+        <v>0.01498517776911473</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01925419454880067</v>
+        <v>0.01925419454880289</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01706990097649674</v>
+        <v>0.01706990097650406</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01581515399969415</v>
+        <v>0.01581515399969567</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01774658737825604</v>
+        <v>0.01774658737825606</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01522465309735906</v>
+        <v>0.01522465309736934</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01706990097649674</v>
+        <v>0.01706990097650406</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01706990097649674</v>
+        <v>0.01706990097650406</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01429373504867248</v>
+        <v>0.01429373504867734</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01706990097649674</v>
+        <v>0.01706990097650406</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01706990097649674</v>
+        <v>0.01706990097650406</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01648620294747903</v>
+        <v>0.01648620294747907</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01545389172410373</v>
+        <v>0.01545389172410953</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01362045628121102</v>
+        <v>0.01362045628121276</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0135115982644627</v>
+        <v>0.01351159826446949</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01457548207745134</v>
+        <v>0.01457548207745997</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01706990097649674</v>
+        <v>0.01706990097650406</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01706990097649674</v>
+        <v>0.01706990097650406</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01706990097649674</v>
+        <v>0.01706990097650406</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01377496593916295</v>
+        <v>0.01377496593917286</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01289302226548088</v>
+        <v>0.01289302226548041</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01479278186718044</v>
+        <v>0.01479278186719106</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01248902228476399</v>
+        <v>0.01248902228477634</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01914289798798228</v>
+        <v>0.01914289798798419</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01494645296525862</v>
+        <v>0.01494645296526992</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01706990097649674</v>
+        <v>0.01706990097650406</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01858864802566183</v>
+        <v>0.0185886480256619</v>
       </c>
     </row>
   </sheetData>
@@ -6742,82 +6742,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02041012636431293</v>
+        <v>0.02041012636432107</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7744133219702298</v>
+        <v>0.7744133219702304</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3050066339894721</v>
+        <v>0.3050066339894781</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6277855805358258</v>
+        <v>0.6277855805358266</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9789901855756155</v>
+        <v>0.9789901855756149</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08867953496254993</v>
+        <v>0.08867953496255709</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1519081106584909</v>
+        <v>0.1519081106584965</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2888505843753459</v>
+        <v>0.2888505843753512</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1990280892219977</v>
+        <v>0.1990280892219994</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2251203234143361</v>
+        <v>0.2251203234143414</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2553707923555576</v>
+        <v>0.2553707923555626</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3890040030981921</v>
+        <v>0.3890040030981924</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04512628796207738</v>
+        <v>0.0451262879620798</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1217548515055948</v>
+        <v>0.1217548515056027</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1718824268382022</v>
+        <v>0.1718824268382073</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03571578871492789</v>
+        <v>0.03571578871493328</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2421661824720236</v>
+        <v>0.2421661824720311</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2812806713777017</v>
+        <v>0.2812806713777088</v>
       </c>
       <c r="T2" t="n">
-        <v>0.07366397136113048</v>
+        <v>0.07366397136113295</v>
       </c>
       <c r="U2" t="n">
-        <v>0.182030956880382</v>
+        <v>0.1820309568803911</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1816682971829287</v>
+        <v>0.1816682971829286</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1343339620159311</v>
+        <v>0.1343339620159373</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2554600689592924</v>
+        <v>0.2554600689592982</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09193086368557409</v>
+        <v>0.09193086368557597</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.06057258933203079</v>
+        <v>0.06057258933203802</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2475597950224362</v>
+        <v>0.2475597950224427</v>
       </c>
       <c r="AB2" t="n">
         <v>0.1467022537373122</v>
@@ -6830,85 +6830,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01764143007839503</v>
+        <v>0.01764143007840192</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02529467130618777</v>
+        <v>0.02529467130618772</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02329490726478497</v>
+        <v>0.02329490726479107</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01999583624197045</v>
+        <v>0.01999583624197047</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02103049219082858</v>
+        <v>0.0210304921908286</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02446719258829997</v>
+        <v>0.02446719258830842</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02329490726478497</v>
+        <v>0.02329490726479107</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02329490726478497</v>
+        <v>0.02329490726479107</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0228272504475007</v>
+        <v>0.02282725044750262</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02329490726478497</v>
+        <v>0.02329490726479107</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02329490726478497</v>
+        <v>0.02329490726479107</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02344800913498913</v>
+        <v>0.02344800913498915</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01891251663900844</v>
+        <v>0.01891251663901183</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02011683563421707</v>
+        <v>0.02011683563422277</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01982162794810712</v>
+        <v>0.0198216279481175</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01653039277718774</v>
+        <v>0.01653039277719906</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02329490726478497</v>
+        <v>0.02329490726479107</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02329490726478497</v>
+        <v>0.02329490726479107</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02329490726478497</v>
+        <v>0.02329490726479107</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02053642133871036</v>
+        <v>0.02053642133871514</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02050198385255273</v>
+        <v>0.02050198385255276</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0232960183342361</v>
+        <v>0.02329601833424395</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01704854519445841</v>
+        <v>0.0170485451944617</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02891757201260238</v>
+        <v>0.02891757201260881</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01753641383724485</v>
+        <v>0.01753641383725101</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02329490726478497</v>
+        <v>0.02329490726479107</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02877659542162655</v>
+        <v>0.02877659542162661</v>
       </c>
     </row>
     <row r="4">
@@ -6918,85 +6918,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0393760163351427</v>
+        <v>0.03937601633515354</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3154722007116906</v>
+        <v>0.3154722007116919</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1431081014636006</v>
+        <v>0.1431081014636062</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2605737260919663</v>
+        <v>0.2605737260919666</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3903612562543578</v>
+        <v>0.39036125625436</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06425941410933307</v>
+        <v>0.06425941410934105</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08730548748308178</v>
+        <v>0.08730548748308388</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1372194110931617</v>
+        <v>0.1372194110931715</v>
       </c>
       <c r="J4" t="n">
-        <v>0.104080781181428</v>
+        <v>0.1040807811814299</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1139904793313811</v>
+        <v>0.1139904793313871</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1250164200415163</v>
+        <v>0.1250164200415238</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1738214541931503</v>
+        <v>0.1738214541931506</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04838476700570808</v>
+        <v>0.04838476700571717</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07631497859929738</v>
+        <v>0.07631497859930714</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09458589118032504</v>
+        <v>0.09458589118033191</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0449547505337839</v>
+        <v>0.0449547505337911</v>
       </c>
       <c r="R4" t="n">
-        <v>0.120203494795325</v>
+        <v>0.1202034947953326</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1344602666959295</v>
+        <v>0.1344602666959349</v>
       </c>
       <c r="T4" t="n">
-        <v>0.05878641749826405</v>
+        <v>0.05878641749826917</v>
       </c>
       <c r="U4" t="n">
-        <v>0.09828491121064312</v>
+        <v>0.09828491121065117</v>
       </c>
       <c r="V4" t="n">
-        <v>0.09667739828867446</v>
+        <v>0.09667739828867346</v>
       </c>
       <c r="W4" t="n">
-        <v>0.08089991666894458</v>
+        <v>0.0808999166689494</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1250489603152389</v>
+        <v>0.1250489603152465</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06544448524984574</v>
+        <v>0.06544448524985416</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05401476247542875</v>
+        <v>0.05401476247543543</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1221694032349563</v>
+        <v>0.122169403234963</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.08513865751555709</v>
+        <v>0.08513865751555755</v>
       </c>
     </row>
     <row r="5">
@@ -7006,85 +7006,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03836685905060466</v>
+        <v>0.0383668590506095</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04242724913996477</v>
+        <v>0.0424272491399653</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04042748509856715</v>
+        <v>0.04042748509856792</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03904150132436614</v>
+        <v>0.03904150132436666</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04119619694625785</v>
+        <v>0.04119619694625836</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04085476933331492</v>
+        <v>0.04085476933332172</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04042748509856715</v>
+        <v>0.04042748509856792</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04042748509856715</v>
+        <v>0.04042748509856792</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03985764450283334</v>
+        <v>0.03985764450283592</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04042748509856715</v>
+        <v>0.04042748509856792</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04042748509856715</v>
+        <v>0.04042748509856792</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0405805869687661</v>
+        <v>0.04058058696876651</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03883015517609819</v>
+        <v>0.03883015517609927</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03926911530802323</v>
+        <v>0.03926911530802586</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03916151557293814</v>
+        <v>0.03916151557294319</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03796189900077628</v>
+        <v>0.0379618990007789</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04042748509856715</v>
+        <v>0.04042748509856792</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04042748509856715</v>
+        <v>0.04042748509856792</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04042748509856715</v>
+        <v>0.04042748509856792</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03942204937028671</v>
+        <v>0.03942204937028829</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03793416959015244</v>
+        <v>0.03793416959015145</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04042789007033142</v>
+        <v>0.04042789007033652</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03815075947241001</v>
+        <v>0.03815075947241934</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04247688037448186</v>
+        <v>0.04247688037448428</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03832858186386869</v>
+        <v>0.03832858186387417</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04042748509856715</v>
+        <v>0.04042748509856792</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0421561398124831</v>
+        <v>0.04215613981248292</v>
       </c>
     </row>
     <row r="6">
@@ -7094,85 +7094,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01527502520432289</v>
+        <v>0.01527502520433039</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2913712095808692</v>
+        <v>0.2913712095808691</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1190071103327777</v>
+        <v>0.119007110332781</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2364727349611436</v>
+        <v>0.2364727349611438</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3662602651235385</v>
+        <v>0.3662602651235382</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03787941080333992</v>
+        <v>0.0378794108033499</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06320449635226205</v>
+        <v>0.06320449635226381</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1131184199623399</v>
+        <v>0.1131184199623466</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07787992695170605</v>
+        <v>0.07787992695170702</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08988948820055959</v>
+        <v>0.08988948820056439</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1009154289106942</v>
+        <v>0.1009154289107016</v>
       </c>
       <c r="M6" t="n">
         <v>0.1497204630623279</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02428377587488717</v>
+        <v>0.02428377587489497</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04993497529330562</v>
+        <v>0.04993497529331214</v>
       </c>
       <c r="P6" t="n">
-        <v>0.06820588787433207</v>
+        <v>0.06820588787433882</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02085375940296193</v>
+        <v>0.02085375940296677</v>
       </c>
       <c r="R6" t="n">
-        <v>0.09610250366450428</v>
+        <v>0.09610250366450748</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1103592755651047</v>
+        <v>0.1103592755651119</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03468542636744324</v>
+        <v>0.03468542636745028</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0719049079046491</v>
+        <v>0.07190490790466007</v>
       </c>
       <c r="V6" t="n">
-        <v>0.07108390592977477</v>
+        <v>0.07108390592977484</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0545199133629494</v>
+        <v>0.05451991336295812</v>
       </c>
       <c r="X6" t="n">
-        <v>0.09866895700924691</v>
+        <v>0.09866895700925324</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.04134349411902403</v>
+        <v>0.04134349411903219</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02991377134460773</v>
+        <v>0.02991377134461108</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.09806841210413267</v>
+        <v>0.09806841210413821</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.06103766638473556</v>
+        <v>0.06103766638473558</v>
       </c>
     </row>
     <row r="7">
@@ -7182,85 +7182,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0142658679197848</v>
+        <v>0.01426586791978525</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01832625800914306</v>
+        <v>0.01832625800914309</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01632649396774311</v>
+        <v>0.01632649396774469</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01494051019354451</v>
+        <v>0.01494051019354452</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01709520581543601</v>
+        <v>0.01709520581543602</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01447476602732089</v>
+        <v>0.01447476602732652</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01632649396774311</v>
+        <v>0.01632649396774469</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01632649396774311</v>
+        <v>0.01632649396774469</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01365679027311144</v>
+        <v>0.01365679027311349</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01632649396774311</v>
+        <v>0.01632649396774469</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01632649396774311</v>
+        <v>0.01632649396774469</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01647959583794428</v>
+        <v>0.0164795958379443</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01472916404527729</v>
+        <v>0.01472916404527505</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01288911200202823</v>
+        <v>0.01288911200203381</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01278151226694517</v>
+        <v>0.01278151226695103</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0138609078699535</v>
+        <v>0.01386090786995371</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01632649396774311</v>
+        <v>0.01632649396774469</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01632649396774311</v>
+        <v>0.01632649396774469</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01632649396774311</v>
+        <v>0.01632649396774469</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01304204606429374</v>
+        <v>0.01304204606429722</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01234067723125291</v>
+        <v>0.01234067723125293</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01404788676433944</v>
+        <v>0.01404788676434232</v>
       </c>
       <c r="X7" t="n">
-        <v>0.011770756166418</v>
+        <v>0.01177075616642822</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01837588924366106</v>
+        <v>0.01837588924366012</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01422759073304669</v>
+        <v>0.01422759073304885</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01632649396774311</v>
+        <v>0.01632649396774469</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01805514868166121</v>
+        <v>0.01805514868166122</v>
       </c>
     </row>
   </sheetData>
